--- a/策划/excel/2_Card.xlsx
+++ b/策划/excel/2_Card.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27765" windowHeight="13485"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27765" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="2_Card" state="visible" r:id="rId4"/>
@@ -781,6 +781,7 @@
     <col min="1" max="1" width="15.5916666666667" customWidth="1"/>
     <col min="3" max="3" width="13.3583333333333" customWidth="1"/>
     <col min="4" max="4" width="15.0916666666667" customWidth="1"/>
+    <col min="8" max="8" width="24.5166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -990,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1">
         <v>10001</v>
@@ -1025,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G7" s="1">
         <v>10001</v>
@@ -1060,7 +1061,7 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1">
         <v>10001</v>
@@ -1095,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1">
         <v>10001</v>
@@ -1130,7 +1131,7 @@
         <v>2</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1">
         <v>10001</v>
@@ -1165,7 +1166,7 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G11" s="1">
         <v>10001</v>
@@ -1200,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G12" s="1">
         <v>10001</v>
@@ -1235,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G13" s="1">
         <v>10001</v>
@@ -1270,7 +1271,7 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G14" s="1">
         <v>10001</v>
@@ -1305,7 +1306,7 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G15">
         <v>10001</v>
@@ -1340,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G16">
         <v>10002</v>
@@ -1375,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G17">
         <v>10002</v>
@@ -1410,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G18">
         <v>10002</v>
@@ -1445,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G19">
         <v>10002</v>
@@ -1480,7 +1481,7 @@
         <v>2</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>10002</v>
@@ -1515,7 +1516,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>10002</v>
@@ -1550,7 +1551,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>10002</v>
@@ -1585,7 +1586,7 @@
         <v>3</v>
       </c>
       <c r="F23">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G23">
         <v>10002</v>
@@ -1620,7 +1621,7 @@
         <v>3</v>
       </c>
       <c r="F24">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G24">
         <v>10002</v>
@@ -1655,7 +1656,7 @@
         <v>3</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G25">
         <v>10002</v>
@@ -1690,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G26">
         <v>10003</v>
@@ -1725,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G27">
         <v>10003</v>
@@ -1760,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G28">
         <v>10003</v>
@@ -1795,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G29">
         <v>10003</v>
@@ -1830,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="F30">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>10003</v>
@@ -1865,7 +1866,7 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>10003</v>
@@ -1900,7 +1901,7 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>10003</v>
@@ -1935,7 +1936,7 @@
         <v>3</v>
       </c>
       <c r="F33">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G33">
         <v>10003</v>
@@ -1970,7 +1971,7 @@
         <v>3</v>
       </c>
       <c r="F34">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G34">
         <v>10003</v>
@@ -2005,7 +2006,7 @@
         <v>3</v>
       </c>
       <c r="F35">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G35">
         <v>10003</v>

--- a/策划/excel/2_Card.xlsx
+++ b/策划/excel/2_Card.xlsx
@@ -996,8 +996,10 @@
       <c r="G6" s="1">
         <v>10001</v>
       </c>
-      <c r="H6" t="s">
-        <v>33</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_1","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I6" t="s">
         <v>34</v>
@@ -1031,8 +1033,10 @@
       <c r="G7" s="1">
         <v>10001</v>
       </c>
-      <c r="H7" t="s">
-        <v>40</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[{"id":"e_starter_1","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I7" t="s">
         <v>41</v>
@@ -1066,8 +1070,10 @@
       <c r="G8" s="1">
         <v>10001</v>
       </c>
-      <c r="H8" t="s">
-        <v>46</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[{"id":"e_starter_2","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I8" t="s">
         <v>34</v>
@@ -1101,8 +1107,10 @@
       <c r="G9" s="1">
         <v>10001</v>
       </c>
-      <c r="H9" t="s">
-        <v>50</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[{"id":"e_starter_3","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_4","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1136,8 +1144,10 @@
       <c r="G10" s="1">
         <v>10001</v>
       </c>
-      <c r="H10" t="s">
-        <v>54</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_6","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_10","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.block","cmp":"&gt;=","rhs":8}]},"children":[{"id":"e_card_7","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_8","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_9","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]}]</t>
+        </is>
       </c>
       <c r="I10" t="s">
         <v>34</v>
@@ -1171,8 +1181,10 @@
       <c r="G11" s="1">
         <v>10001</v>
       </c>
-      <c r="H11" t="s">
-        <v>58</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_11","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_14","type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_12","type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_13","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I11" t="s">
         <v>41</v>
@@ -1206,8 +1218,10 @@
       <c r="G12" s="1">
         <v>10001</v>
       </c>
-      <c r="H12" t="s">
-        <v>63</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_16","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_15","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_17","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I12" t="s">
         <v>34</v>
@@ -1241,8 +1255,10 @@
       <c r="G13" s="1">
         <v>10001</v>
       </c>
-      <c r="H13" t="s">
-        <v>67</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_22","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;=","rhs":50}]},"children":[{"id":"e_card_19","type":210003,"target":"SELF","params":{"amount":8},"children":[],"elseEffects":[]},{"id":"e_card_20","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_21","type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[]}]},{"id":"e_card_25","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_23","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]},{"id":"e_rebalance_3","type":210003,"target":"SELF","params":{"amount":4},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I13" t="s">
         <v>41</v>
@@ -1276,8 +1292,10 @@
       <c r="G14" s="1">
         <v>10001</v>
       </c>
-      <c r="H14" t="s">
-        <v>71</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_26","type":210015,"target":"SELF","params":{"stat":200001,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_27","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_30","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_28","type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_29","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I14" t="s">
         <v>41</v>
@@ -1311,8 +1329,10 @@
       <c r="G15">
         <v>10001</v>
       </c>
-      <c r="H15" t="s">
-        <v>75</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_40","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":3},"children":[{"id":"e_card_33","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_31","type":210002,"target":"SELF","params":{"amount":16,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_32","type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_36","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_34","type":210001,"target":"ENEMY","params":{"amount":12,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_35","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_39","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_37","type":210003,"target":"SELF","params":{"amount":10},"children":[],"elseEffects":[]},{"id":"e_rebalance_4","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I15" t="s">
         <v>41</v>
@@ -1346,8 +1366,10 @@
       <c r="G16">
         <v>10002</v>
       </c>
-      <c r="H16" t="s">
-        <v>78</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_41","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I16" t="s">
         <v>34</v>
@@ -1381,8 +1403,10 @@
       <c r="G17">
         <v>10002</v>
       </c>
-      <c r="H17" t="s">
-        <v>81</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_42","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I17" t="s">
         <v>41</v>
@@ -1416,8 +1440,10 @@
       <c r="G18">
         <v>10002</v>
       </c>
-      <c r="H18" t="s">
-        <v>84</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_43","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I18" t="s">
         <v>34</v>
@@ -1451,8 +1477,10 @@
       <c r="G19">
         <v>10002</v>
       </c>
-      <c r="H19" t="s">
-        <v>88</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[{"id":"e_starter_5","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_6","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I19" t="s">
         <v>34</v>
@@ -1486,8 +1514,10 @@
       <c r="G20">
         <v>10002</v>
       </c>
-      <c r="H20" t="s">
-        <v>92</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_46","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_45","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_rebalance_6","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_48","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I20" t="s">
         <v>34</v>
@@ -1521,8 +1551,10 @@
       <c r="G21">
         <v>10002</v>
       </c>
-      <c r="H21" t="s">
-        <v>96</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_49","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_50","type":210026,"target":"SELF","params":{"count":1,"mode":"SELECT","filter":{}},"children":[],"elseEffects":[]},{"id":"e_card_53","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":30}]},"children":[{"id":"e_card_51","type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_rebalance_7","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+        </is>
       </c>
       <c r="I21" t="s">
         <v>34</v>
@@ -1556,8 +1588,10 @@
       <c r="G22">
         <v>10002</v>
       </c>
-      <c r="H22" t="s">
-        <v>100</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[{"id":"e_rebalance_8","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_57","type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_55","type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_56","type":210002,"target":"SELF","params":{"amount":2,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I22" t="s">
         <v>41</v>
@@ -1591,8 +1625,10 @@
       <c r="G23">
         <v>10002</v>
       </c>
-      <c r="H23" t="s">
-        <v>104</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_65","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":2},"children":[{"id":"e_card_61","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_59","type":210021,"target":"ENEMY","params":{"count":4,"maxIterations":10},"children":[{"id":"e_card_58","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_60","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_64","type":210020,"target":"SELF","params":{},"children":[{"id":"e_rebalance_9","type":210015,"target":"SELF","params":{"stat":200002,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_63","type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I23" t="s">
         <v>41</v>
@@ -1626,8 +1662,10 @@
       <c r="G24">
         <v>10002</v>
       </c>
-      <c r="H24" t="s">
-        <v>108</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_66","type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]},{"id":"e_rebalance_10","type":210015,"target":"SELF","params":{"stat":200002,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_70","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_rebalance_11","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_69","type":210001,"target":"ENEMY","params":{"amount":6,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I24" t="s">
         <v>41</v>
@@ -1661,8 +1699,10 @@
       <c r="G25">
         <v>10002</v>
       </c>
-      <c r="H25" t="s">
-        <v>112</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_76","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":18}]},"children":[{"id":"e_card_71","type":210005,"target":"ENEMY","params":{"threshold":18},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_73","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_72","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_74","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_12","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+        </is>
       </c>
       <c r="I25" t="s">
         <v>34</v>
@@ -1696,8 +1736,10 @@
       <c r="G26">
         <v>10003</v>
       </c>
-      <c r="H26" t="s">
-        <v>115</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_77","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I26" t="s">
         <v>34</v>
@@ -1731,8 +1773,10 @@
       <c r="G27">
         <v>10003</v>
       </c>
-      <c r="H27" t="s">
-        <v>118</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[{"id":"e_starter_8","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I27" t="s">
         <v>41</v>
@@ -1766,8 +1810,10 @@
       <c r="G28">
         <v>10003</v>
       </c>
-      <c r="H28" t="s">
-        <v>121</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[{"id":"e_starter_7","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I28" t="s">
         <v>34</v>
@@ -1801,8 +1847,10 @@
       <c r="G29">
         <v>10003</v>
       </c>
-      <c r="H29" t="s">
-        <v>125</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[{"id":"e_starter_9","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_10","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I29" t="s">
         <v>34</v>
@@ -1836,8 +1884,10 @@
       <c r="G30">
         <v>10003</v>
       </c>
-      <c r="H30" t="s">
-        <v>129</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_81","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_82","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_86","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.buff.200006","cmp":"&gt;=","rhs":3}]},"children":[{"id":"e_card_83","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_rebalance_14","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_85","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+        </is>
       </c>
       <c r="I30" t="s">
         <v>34</v>
@@ -1871,8 +1921,10 @@
       <c r="G31">
         <v>10003</v>
       </c>
-      <c r="H31" t="s">
-        <v>133</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_87","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_91","type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_rebalance_15","type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_89","type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]},{"id":"e_card_90","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I31" t="s">
         <v>41</v>
@@ -1906,8 +1958,10 @@
       <c r="G32">
         <v>10003</v>
       </c>
-      <c r="H32" t="s">
-        <v>137</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_93","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_92","type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_94","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_16","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I32" t="s">
         <v>34</v>
@@ -1941,8 +1995,10 @@
       <c r="G33">
         <v>10003</v>
       </c>
-      <c r="H33" t="s">
-        <v>141</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_105","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":3},"children":[{"id":"e_card_98","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_96","type":210031,"target":"SELF","params":{"amount":25},"children":[],"elseEffects":[]},{"id":"e_rebalance_17","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_101","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_99","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":4,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_100","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_104","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_102","type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"id":"e_card_103","type":210003,"target":"SELF","params":{"amount":12},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I33" t="s">
         <v>41</v>
@@ -1976,8 +2032,10 @@
       <c r="G34">
         <v>10003</v>
       </c>
-      <c r="H34" t="s">
-        <v>145</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_106","type":210031,"target":"SELF","params":{"amount":15},"children":[],"elseEffects":[]},{"id":"e_card_107","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_111","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.gold","cmp":"&gt;=","rhs":30}]},"children":[{"id":"e_card_108","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_18","type":210003,"target":"SELF","params":{"amount":5},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_110","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+        </is>
       </c>
       <c r="I34" t="s">
         <v>34</v>
@@ -2011,8 +2069,10 @@
       <c r="G35">
         <v>10003</v>
       </c>
-      <c r="H35" t="s">
-        <v>149</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[{"id":"e_card_112","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":5,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_114","type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_113","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_117","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_115","type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]},{"id":"e_rebalance_19","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="I35" t="s">
         <v>34</v>

--- a/策划/excel/2_Card.xlsx
+++ b/策划/excel/2_Card.xlsx
@@ -1,20 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\策划\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27765" windowHeight="10815"/>
+    <workbookView windowWidth="30435" windowHeight="15735"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="2_Card" state="visible" r:id="rId4"/>
+    <sheet name="2_Card" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="373">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -106,395 +124,1466 @@
     <t>client</t>
   </si>
   <si>
-    <t>巨剑斩</t>
+    <t>浪刺</t>
   </si>
   <si>
     <t>造成6点伤害。</t>
   </si>
   <si>
+    <t>[30005]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_41","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>ENEMY</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>回身步</t>
+  </si>
+  <si>
+    <t>获得5点格挡。</t>
+  </si>
+  <si>
+    <t>[30006]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_42","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>SELF</t>
+  </si>
+  <si>
+    <t>SKILL</t>
+  </si>
+  <si>
+    <t>残月刃</t>
+  </si>
+  <si>
+    <t>造成两次3点伤害。</t>
+  </si>
+  <si>
+    <t>[30007]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_43","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>断潮</t>
+  </si>
+  <si>
+    <t>造成8点伤害，施加2回合虚弱。</t>
+  </si>
+  <si>
+    <t>[30005,30008]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_starter_5","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_6","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>海潮连舞</t>
+  </si>
+  <si>
+    <t>连续攻击3次，每次4点；施加1层虚弱并获得4点格挡。</t>
+  </si>
+  <si>
+    <t>[30005,30006]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_46","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_45","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_rebalance_6","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_48","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>破浪回旋</t>
+  </si>
+  <si>
+    <t>攻击8点并弃1张牌；若敌人生命不高于30，再攻击两次，否则获得8点格挡。</t>
+  </si>
+  <si>
+    <t>[30006,30007,30005]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_49","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_50","type":210026,"target":"SELF","params":{"count":1,"mode":"SELECT","filter":{}},"children":[],"elseEffects":[]},{"id":"e_card_53","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":30}]},"children":[{"id":"e_card_51","type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_rebalance_7","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+  </si>
+  <si>
+    <t>逐影杀机</t>
+  </si>
+  <si>
+    <t>获得1点力量；本场战斗每打出一张攻击牌，追加3点伤害并获得2点格挡。</t>
+  </si>
+  <si>
+    <t>[30007,30005,30008]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_rebalance_8","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_57","type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_55","type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_56","type":210002,"target":"SELF","params":{"amount":2,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>POWER</t>
+  </si>
+  <si>
+    <t>月刃双途</t>
+  </si>
+  <si>
+    <t>选择连斩或蓄势：连斩攻击四次并施加虚弱；蓄势获得2点敏捷和10点格挡。</t>
+  </si>
+  <si>
+    <t>[30007,30007,30006]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_65","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":2},"children":[{"id":"e_card_61","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_59","type":210021,"target":"ENEMY","params":{"count":4,"maxIterations":10},"children":[{"id":"e_card_58","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_60","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_64","type":210020,"target":"SELF","params":{},"children":[{"id":"e_rebalance_9","type":210015,"target":"SELF","params":{"stat":200002,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_63","type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>潮汐预备</t>
+  </si>
+  <si>
+    <t>获得10点格挡与1点敏捷；下回合再获得6点格挡并攻击两次。</t>
+  </si>
+  <si>
+    <t>[30006,30008,30007,30005]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_66","type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]},{"id":"e_rebalance_10","type":210015,"target":"SELF","params":{"stat":200002,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_70","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_rebalance_11","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_69","type":210001,"target":"ENEMY","params":{"amount":6,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>断月终曲</t>
+  </si>
+  <si>
+    <t>若敌人生命不高于18则直接击杀；否则攻击三次、施加易伤并获得6点格挡。</t>
+  </si>
+  <si>
+    <t>[30005,30007,30008,30007]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_76","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":18}]},"children":[{"id":"e_card_71","type":210005,"target":"ENEMY","params":{"threshold":18},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_73","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_72","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_74","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_12","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+  </si>
+  <si>
+    <t>匕首突袭</t>
+  </si>
+  <si>
+    <t>[30009]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_77","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>披风掩护</t>
+  </si>
+  <si>
+    <t>[30010]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_starter_8","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>羽刃连刺</t>
+  </si>
+  <si>
+    <t>[30011]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_starter_7","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>猎手毒袭</t>
+  </si>
+  <si>
+    <t>造成8点伤害，施加3层中毒。</t>
+  </si>
+  <si>
+    <t>[30009,30012]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_starter_9","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_10","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>毒刃追击</t>
+  </si>
+  <si>
+    <t>施加3层中毒并攻击7点；若敌人中毒达到3层，再攻击5点并追加1层中毒。</t>
+  </si>
+  <si>
+    <t>[30009,30011]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_81","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_82","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_86","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.buff.200006","cmp":"&gt;=","rhs":3}]},"children":[{"id":"e_card_83","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_rebalance_14","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_85","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+  </si>
+  <si>
+    <t>雾隐反制</t>
+  </si>
+  <si>
+    <t>获得8点格挡；本场战斗受到伤害时再次获得3点格挡、回复3点并反击4点。</t>
+  </si>
+  <si>
+    <t>[30010,30011,30010]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_87","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_91","type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_rebalance_15","type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_89","type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]},{"id":"e_card_90","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>投羽连击</t>
+  </si>
+  <si>
+    <t>连续攻击3次，每次3点；施加2层虚弱，随后获得5点格挡。</t>
+  </si>
+  <si>
+    <t>[30011,30009,30011]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_93","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_92","type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_94","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_16","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>偷天换日</t>
+  </si>
+  <si>
+    <t>选择盗财、制敌或休整：分别获得金币与格挡、施毒并攻击、净化并回复。</t>
+  </si>
+  <si>
+    <t>[30012,30009,30010,30011]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_105","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":3},"children":[{"id":"e_card_98","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_96","type":210031,"target":"SELF","params":{"amount":25},"children":[],"elseEffects":[]},{"id":"e_rebalance_17","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_101","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_99","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":4,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_100","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_104","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_102","type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"id":"e_card_103","type":210003,"target":"SELF","params":{"amount":12},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>钱袋伏击</t>
+  </si>
+  <si>
+    <t>获得15金币并攻击10点；若自身金币达到30，再施加易伤并回复5点，否则获得8点格挡。</t>
+  </si>
+  <si>
+    <t>[30012,30009,30012,30010]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_106","type":210031,"target":"SELF","params":{"amount":15},"children":[],"elseEffects":[]},{"id":"e_card_107","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_111","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.gold","cmp":"&gt;=","rhs":30}]},"children":[{"id":"e_card_108","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_18","type":210003,"target":"SELF","params":{"amount":5},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_110","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}]}]</t>
+  </si>
+  <si>
+    <t>游侠终咒</t>
+  </si>
+  <si>
+    <t>施加5层中毒；本场战斗每回合结束追加4点伤害，下回合回复6点并获得8点格挡。</t>
+  </si>
+  <si>
+    <t>[30009,30010,30011,30012]</t>
+  </si>
+  <si>
+    <t>[{"id":"e_card_112","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":5,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_114","type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_113","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_117","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_115","type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]},{"id":"e_rebalance_19","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+  </si>
+  <si>
+    <t>痛击</t>
+  </si>
+  <si>
+    <t>造成8点伤害。
+给予2层易伤。</t>
+  </si>
+  <si>
+    <t>[30003,30003]</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect1"},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect2"}]</t>
+  </si>
+  <si>
+    <t>{"starterOnly":true}</t>
+  </si>
+  <si>
+    <t>打击</t>
+  </si>
+  <si>
+    <t>[30003]</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect3"}]</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>[30002]</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect4"}]</t>
+  </si>
+  <si>
+    <t>愤怒</t>
+  </si>
+  <si>
+    <t>造成6点伤害。
+将一张此牌的复制品加入你的弃牌堆。</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect5"},{"type":210042,"target":"SELF","params":{"source":"THIS","pile":"DISCARD"},"children":[],"elseEffects":[],"id":"warriorEffect6"}]</t>
+  </si>
+  <si>
+    <t>全身撞击</t>
+  </si>
+  <si>
+    <t>造成你当前格挡值的伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":"@self.block","hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect7"}]</t>
+  </si>
+  <si>
+    <t>突破</t>
+  </si>
+  <si>
+    <t>失去1点生命。
+对敌人造成9点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210004,"target":"SELF","params":{"amount":1,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect8"},{"type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect9"}]</t>
+  </si>
+  <si>
+    <t>余烬</t>
+  </si>
+  <si>
+    <t>造成18点伤害。
+随机消耗1张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":18,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect10"},{"type":210027,"target":"SELF","params":{"count":1,"zone":"HAND","mode":"RANDOM","filter":{}},"children":[],"elseEffects":[],"id":"warriorEffect11"}]</t>
+  </si>
+  <si>
+    <t>头槌</t>
+  </si>
+  <si>
+    <t>造成6点伤害。
+将弃牌堆中的1张牌放到抽牌堆顶部。</t>
+  </si>
+  <si>
     <t>[30001]</t>
   </si>
   <si>
-    <t>[{"id":"e_card_1","type":"DAMAGE","target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]</t>
-  </si>
-  <si>
-    <t>ENEMY</t>
-  </si>
-  <si>
-    <t>ATTACK</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>猫纹盾</t>
-  </si>
-  <si>
-    <t>获得5点格挡。</t>
-  </si>
-  <si>
-    <t>[30003]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_starter_1","type":"BLOCK","target":"SELF","params":{"amount":5}}]</t>
-  </si>
-  <si>
-    <t>SELF</t>
-  </si>
-  <si>
-    <t>SKILL</t>
-  </si>
-  <si>
-    <t>印记连斩</t>
-  </si>
-  <si>
-    <t>造成两次3点伤害。</t>
-  </si>
-  <si>
-    <t>[30002]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_starter_2","type":"DAMAGE","target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false}}]</t>
-  </si>
-  <si>
-    <t>爪痕破甲</t>
-  </si>
-  <si>
-    <t>造成8点伤害，施加2回合易伤。</t>
-  </si>
-  <si>
-    <t>[30001,30004]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_starter_3","type":"DAMAGE","target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_starter_4","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":2,"duration":"DEFAULT"}}]</t>
-  </si>
-  <si>
-    <t>盾锋冲撞</t>
-  </si>
-  <si>
-    <t>获得8点格挡；若格挡达到8点，再造成9点伤害并施加1层易伤。</t>
-  </si>
-  <si>
-    <t>[30003,30001]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_6","type":"BLOCK","target":"SELF","params":{"amount":8}},{"id":"e_card_10","type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.block","cmp":"&gt;=","rhs":8}]},"children":[{"id":"e_card_7","type":"DAMAGE","target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_8","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}],"elseEffects":[{"id":"e_card_9","type":"DAMAGE","target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]}]</t>
-  </si>
-  <si>
-    <t>反击架势</t>
-  </si>
-  <si>
-    <t>获得6点格挡；本场战斗受到伤害时，再获得3点格挡并反击4点。</t>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect12"},{"type":210041,"target":"SELF","params":{"pile":"DISCARD","destination":"DRAW_TOP","mode":"SELECT"},"children":[],"elseEffects":[],"id":"warriorEffect13"}]</t>
+  </si>
+  <si>
+    <t>铁斩波</t>
+  </si>
+  <si>
+    <t>获得6点格挡。
+造成3点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect14"},{"type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect15"}]</t>
+  </si>
+  <si>
+    <t>熔融之拳</t>
+  </si>
+  <si>
+    <t>造成10点伤害。
+将该敌人身上的易伤层数翻倍。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect16"},{"type":210012,"target":"ENEMY","params":{"status":200004,"factor":2},"children":[],"elseEffects":[],"id":"warriorEffect17"}]</t>
+  </si>
+  <si>
+    <t>{"exhaust":true}</t>
+  </si>
+  <si>
+    <t>完美打击</t>
+  </si>
+  <si>
+    <t>造成6点伤害。
+你每有一张名字中含有“打击”的牌，伤害+2。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":"6+2*@battle.strikeCount","hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect18"}]</t>
+  </si>
+  <si>
+    <t>剑柄打击</t>
+  </si>
+  <si>
+    <t>造成6点伤害。
+抽1张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect19"},{"type":210038,"target":"SELF","params":{"count":1,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect20"}]</t>
+  </si>
+  <si>
+    <t>预备打击</t>
+  </si>
+  <si>
+    <t>造成7点伤害。
+在本回合内获得2点力量。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect21"},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":2,"duration":"TURN"},"children":[],"elseEffects":[],"id":"warriorEffect22"}]</t>
+  </si>
+  <si>
+    <t>飞剑回旋镖</t>
+  </si>
+  <si>
+    <t>对敌人造成2点伤害3次。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":2,"hits":3,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect23"}]</t>
+  </si>
+  <si>
+    <t>闪电霹雳</t>
+  </si>
+  <si>
+    <t>造成3点伤害。
+给予敌人1层虚弱。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect24"},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect25"}]</t>
+  </si>
+  <si>
+    <t>双重打击</t>
+  </si>
+  <si>
+    <t>造成3点伤害2次。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect26"}]</t>
+  </si>
+  <si>
+    <t>血墙</t>
+  </si>
+  <si>
+    <t>失去2点生命。
+获得16点格挡。</t>
+  </si>
+  <si>
+    <t>[{"type":210004,"target":"SELF","params":{"amount":2,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect27"},{"type":210002,"target":"SELF","params":{"amount":16,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect28"}]</t>
+  </si>
+  <si>
+    <t>放血</t>
+  </si>
+  <si>
+    <t>失去3点生命。
+获得2点能量。</t>
+  </si>
+  <si>
+    <t>[{"type":210004,"target":"SELF","params":{"amount":3,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect29"},{"type":210037,"target":"SELF","params":{"amount":2},"children":[],"elseEffects":[],"id":"warriorEffect30"}]</t>
+  </si>
+  <si>
+    <t>破灭</t>
+  </si>
+  <si>
+    <t>无需骰子打出抽牌堆顶部的1张牌，结算后将其消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210043,"target":"SELF","params":{"pile":"DRAW","mode":"TOP","exhaustAfter":true},"children":[],"elseEffects":[],"id":"warriorEffect31"}]</t>
+  </si>
+  <si>
+    <t>耸肩无视</t>
+  </si>
+  <si>
+    <t>获得8点格挡。
+抽1张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect32"},{"type":210038,"target":"SELF","params":{"count":1,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect33"}]</t>
+  </si>
+  <si>
+    <t>战栗</t>
+  </si>
+  <si>
+    <t>给予3层易伤。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect34"}]</t>
+  </si>
+  <si>
+    <t>坚毅</t>
+  </si>
+  <si>
+    <t>获得7点格挡。
+随机消耗1张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect35"},{"type":210027,"target":"SELF","params":{"count":1,"zone":"HAND","mode":"RANDOM","filter":{}},"children":[],"elseEffects":[],"id":"warriorEffect36"}]</t>
+  </si>
+  <si>
+    <t>灰烬打击</t>
+  </si>
+  <si>
+    <t>造成6点伤害。
+你的消耗牌堆中每有一张牌，伤害增加3。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":"6+3*@battle.exhaustCount","hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect37"}]</t>
+  </si>
+  <si>
+    <t>重锤</t>
+  </si>
+  <si>
+    <t>造成32点伤害。</t>
+  </si>
+  <si>
+    <t>[30003,30003,30003]</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":32,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect38"}]</t>
+  </si>
+  <si>
+    <t>欺凌</t>
+  </si>
+  <si>
+    <t>造成4点伤害。
+该敌人身上每有一层易伤就额外造成2点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":"4+2*@target.buff.200004","hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect39"}]</t>
+  </si>
+  <si>
+    <t>拆卸</t>
+  </si>
+  <si>
+    <t>造成5点伤害。
+如果敌人有易伤状态，则改为造成2次伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210019,"target":"SELF","params":{},"children":[{"type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect41"}],"elseEffects":[{"type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect42"}],"condition":{"op":"AND","rules":[{"lhs":"@target.buff.200004","cmp":"&gt;","rhs":0}]},"id":"warriorEffect40"}]</t>
+  </si>
+  <si>
+    <t>与我一战！</t>
+  </si>
+  <si>
+    <t>造成5点伤害两次。
+获得3点力量。
+该敌人获得1点力量。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect43"},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":3,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect44"},{"type":210010,"target":"ENEMY","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect45"}]</t>
+  </si>
+  <si>
+    <t>御血术</t>
+  </si>
+  <si>
+    <t>失去2点生命。
+造成15点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210004,"target":"SELF","params":{"amount":2,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect46"},{"type":210001,"target":"ENEMY","params":{"amount":15,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect47"}]</t>
+  </si>
+  <si>
+    <t>彼岸咆哮</t>
+  </si>
+  <si>
+    <t>造成16点伤害。
+回合结束时，若此牌位于消耗牌堆，则无需骰子对当前敌人结算此牌的伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":16,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect48"},{"type":210001,"target":"ENEMY","params":{"amount":16,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"trigger":"ON_TURN_END_IN_EXHAUST","id":"warriorEffect49"}]</t>
+  </si>
+  <si>
+    <t>劫掠</t>
+  </si>
+  <si>
+    <t>造成5点伤害。
+连续抽牌，直到抽到1张非攻击牌或手牌达到10张；无牌可抽时停止。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect50"},{"type":210038,"target":"SELF","params":{"count":100,"untilNonAttack":true},"children":[],"elseEffects":[],"id":"warriorEffect51"}]</t>
+  </si>
+  <si>
+    <t>暴走</t>
+  </si>
+  <si>
+    <t>造成9点伤害。
+将这张牌在本场战斗中的伤害增加5。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect52"},{"type":210046,"target":"SELF","params":{"amount":5},"children":[],"elseEffects":[],"id":"warriorEffect53"}]</t>
+  </si>
+  <si>
+    <t>怨恨</t>
+  </si>
+  <si>
+    <t>造成5点伤害。
+如果你在本回合失去过生命值，
+则攻击2次。</t>
+  </si>
+  <si>
+    <t>[{"type":210019,"target":"SELF","params":{},"children":[{"type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect55"}],"elseEffects":[{"type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect56"}],"condition":{"op":"AND","rules":[{"lhs":"@battle.hpLossThisTurn","cmp":"&gt;","rhs":0}]},"id":"warriorEffect54"}]</t>
+  </si>
+  <si>
+    <t>踩踏</t>
+  </si>
+  <si>
+    <t>造成12点伤害。
+本回合每打出过1张攻击牌，此牌少需要1颗斧头骰子；最多减免2颗斧头骰子，仍需要1颗符文骰子。</t>
+  </si>
+  <si>
+    <t>[30001,30003,30003]</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":12,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect57"}]</t>
+  </si>
+  <si>
+    <t>{"discountDice":30003,"discountMax":2}</t>
+  </si>
+  <si>
+    <t>无情猛攻</t>
+  </si>
+  <si>
+    <t>造成14点伤害。
+你打出的下一张攻击牌无需骰子。</t>
+  </si>
+  <si>
+    <t>[30001,30003]</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":14,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect58"},{"type":210047,"target":"SELF","params":{"kind":"NEXT_ATTACK_FREE","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect59"}]</t>
+  </si>
+  <si>
+    <t>上勾拳</t>
+  </si>
+  <si>
+    <t>造成10点伤害。
+给予敌人1层虚弱。
+给予敌人1层易伤。</t>
   </si>
   <si>
     <t>[30002,30003]</t>
   </si>
   <si>
-    <t>[{"id":"e_card_11","type":"BLOCK","target":"SELF","params":{"amount":6}},{"id":"e_card_14","type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_12","type":"BLOCK","target":"SELF","params":{"amount":3}},{"id":"e_card_13","type":"DAMAGE","target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]}]</t>
-  </si>
-  <si>
-    <t>POWER</t>
-  </si>
-  <si>
-    <t>连爪战技</t>
-  </si>
-  <si>
-    <t>连续攻击3次，每次4点；随后施加2层虚弱并获得4点格挡。</t>
-  </si>
-  <si>
-    <t>[30004,30004,30002]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_16","type":"REPEAT","target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_15","type":"DAMAGE","target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]},{"id":"e_card_17","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":2,"duration":"DEFAULT"}},{"id":"e_rebalance_2","type":"BLOCK","target":"SELF","params":{"amount":4}}]</t>
-  </si>
-  <si>
-    <t>铁盔庇护</t>
-  </si>
-  <si>
-    <t>生命不高于50时回复8点，否则获得12点格挡；下回合再获得6点格挡并回复4点。</t>
-  </si>
-  <si>
-    <t>[30003,30002,30003]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_22","type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;=","rhs":50}]},"children":[{"id":"e_card_19","type":"HEAL","target":"SELF","params":{"amount":8}},{"id":"e_card_20","type":"BLOCK","target":"SELF","params":{"amount":6}}],"elseEffects":[{"id":"e_card_21","type":"BLOCK","target":"SELF","params":{"amount":12}}]},{"id":"e_card_25","type":"SCHEDULE","target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_23","type":"BLOCK","target":"SELF","params":{"amount":6}},{"id":"e_rebalance_3","type":"HEAL","target":"SELF","params":{"amount":4}}]}]</t>
-  </si>
-  <si>
-    <t>巨剑誓约</t>
-  </si>
-  <si>
-    <t>本场战斗获得2点力量并攻击8点；下回合再攻击两次并施加易伤。</t>
-  </si>
-  <si>
-    <t>[30001,30001,30004,30002]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_26","type":"MODIFY_STAT","target":"SELF","params":{"stat":"STRENGTH","amount":2,"duration":"COMBAT"}},{"id":"e_card_27","type":"DAMAGE","target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_30","type":"SCHEDULE","target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_28","type":"DAMAGE","target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_29","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":1,"duration":"DEFAULT"}}]}]</t>
-  </si>
-  <si>
-    <t>王庭抉择</t>
-  </si>
-  <si>
-    <t>选择重盾、破甲或休整：分别获得格挡与净化、攻击与易伤、回复与格挡。</t>
-  </si>
-  <si>
-    <t>[30003,30001,30002,30004]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_40","type":"CHOOSE_ONE","target":"SELF","params":{"maxChoices":1,"showCount":3},"children":[{"id":"e_card_33","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_card_31","type":"BLOCK","target":"SELF","params":{"amount":16}},{"id":"e_card_32","type":"CLEANSE","target":"SELF","params":{"filter":{"kind":"DEBUFF"}}}]},{"id":"e_card_36","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_card_34","type":"DAMAGE","target":"ENEMY","params":{"amount":12,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_35","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":2,"duration":"DEFAULT"}}]},{"id":"e_card_39","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_card_37","type":"HEAL","target":"SELF","params":{"amount":10}},{"id":"e_rebalance_4","type":"BLOCK","target":"SELF","params":{"amount":8}}]}]}]</t>
-  </si>
-  <si>
-    <t>浪刺</t>
-  </si>
-  <si>
-    <t>[30005]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_41","type":"DAMAGE","target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]</t>
-  </si>
-  <si>
-    <t>回身步</t>
-  </si>
-  <si>
-    <t>[30006]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_42","type":"BLOCK","target":"SELF","params":{"amount":5}}]</t>
-  </si>
-  <si>
-    <t>残月刃</t>
-  </si>
-  <si>
-    <t>[30007]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_43","type":"DAMAGE","target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false}}]</t>
-  </si>
-  <si>
-    <t>断潮</t>
-  </si>
-  <si>
-    <t>造成8点伤害，施加2回合虚弱。</t>
-  </si>
-  <si>
-    <t>[30005,30008]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_starter_5","type":"DAMAGE","target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_starter_6","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":2,"duration":"DEFAULT"}}]</t>
-  </si>
-  <si>
-    <t>海潮连舞</t>
-  </si>
-  <si>
-    <t>连续攻击3次，每次4点；施加1层虚弱并获得4点格挡。</t>
-  </si>
-  <si>
-    <t>[30005,30006]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_46","type":"REPEAT","target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_45","type":"DAMAGE","target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]},{"id":"e_rebalance_6","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":1,"duration":"DEFAULT"}},{"id":"e_card_48","type":"BLOCK","target":"SELF","params":{"amount":4}}]</t>
-  </si>
-  <si>
-    <t>破浪回旋</t>
-  </si>
-  <si>
-    <t>攻击8点并弃1张牌；若敌人生命不高于30，再攻击两次，否则获得8点格挡。</t>
-  </si>
-  <si>
-    <t>[30006,30007,30005]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_49","type":"DAMAGE","target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_50","type":"DISCARD","target":"SELF","params":{"count":1,"mode":"SELECT","filter":{}}},{"id":"e_card_53","type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":30}]},"children":[{"id":"e_card_51","type":"DAMAGE","target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false}}],"elseEffects":[{"id":"e_rebalance_7","type":"BLOCK","target":"SELF","params":{"amount":8}}]}]</t>
-  </si>
-  <si>
-    <t>逐影杀机</t>
-  </si>
-  <si>
-    <t>获得1点力量；本场战斗每打出一张攻击牌，追加3点伤害并获得2点格挡。</t>
-  </si>
-  <si>
-    <t>[30007,30005,30008]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_rebalance_8","type":"MODIFY_STAT","target":"SELF","params":{"stat":"STRENGTH","amount":1,"duration":"COMBAT"}},{"id":"e_card_57","type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_55","type":"DAMAGE","target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_56","type":"BLOCK","target":"SELF","params":{"amount":2}}]}]</t>
-  </si>
-  <si>
-    <t>月刃双途</t>
-  </si>
-  <si>
-    <t>选择连斩或蓄势：连斩攻击四次并施加虚弱；蓄势获得2点敏捷和10点格挡。</t>
-  </si>
-  <si>
-    <t>[30007,30007,30006]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_65","type":"CHOOSE_ONE","target":"SELF","params":{"maxChoices":1,"showCount":2},"children":[{"id":"e_card_61","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_card_59","type":"REPEAT","target":"ENEMY","params":{"count":4,"maxIterations":10},"children":[{"id":"e_card_58","type":"DAMAGE","target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]},{"id":"e_card_60","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":2,"duration":"DEFAULT"}}]},{"id":"e_card_64","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_rebalance_9","type":"MODIFY_STAT","target":"SELF","params":{"stat":"DEXTERITY","amount":2,"duration":"COMBAT"}},{"id":"e_card_63","type":"BLOCK","target":"SELF","params":{"amount":10}}]}]}]</t>
-  </si>
-  <si>
-    <t>潮汐预备</t>
-  </si>
-  <si>
-    <t>获得10点格挡与1点敏捷；下回合再获得6点格挡并攻击两次。</t>
-  </si>
-  <si>
-    <t>[30006,30008,30007,30005]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_66","type":"BLOCK","target":"SELF","params":{"amount":10}},{"id":"e_rebalance_10","type":"MODIFY_STAT","target":"SELF","params":{"stat":"DEXTERITY","amount":1,"duration":"COMBAT"}},{"id":"e_card_70","type":"SCHEDULE","target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_rebalance_11","type":"BLOCK","target":"SELF","params":{"amount":6}},{"id":"e_card_69","type":"DAMAGE","target":"ENEMY","params":{"amount":6,"hits":2,"damageKind":"ATTACK","ignoreBlock":false}}]}]</t>
-  </si>
-  <si>
-    <t>断月终曲</t>
-  </si>
-  <si>
-    <t>若敌人生命不高于18则直接击杀；否则攻击三次、施加易伤并获得6点格挡。</t>
-  </si>
-  <si>
-    <t>[30005,30007,30008,30007]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_76","type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":18}]},"children":[{"id":"e_card_71","type":"KILL_IF","target":"ENEMY","params":{"threshold":18}}],"elseEffects":[{"id":"e_card_73","type":"REPEAT","target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_72","type":"DAMAGE","target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]},{"id":"e_card_74","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":2,"duration":"DEFAULT"}},{"id":"e_rebalance_12","type":"BLOCK","target":"SELF","params":{"amount":6}}]}]</t>
-  </si>
-  <si>
-    <t>匕首突袭</t>
-  </si>
-  <si>
-    <t>[30009]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_77","type":"DAMAGE","target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]</t>
-  </si>
-  <si>
-    <t>披风掩护</t>
-  </si>
-  <si>
-    <t>[30010]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_starter_8","type":"BLOCK","target":"SELF","params":{"amount":5}}]</t>
-  </si>
-  <si>
-    <t>羽刃连刺</t>
-  </si>
-  <si>
-    <t>[30011]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_starter_7","type":"DAMAGE","target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false}}]</t>
-  </si>
-  <si>
-    <t>猎手毒袭</t>
-  </si>
-  <si>
-    <t>造成8点伤害，施加3层中毒。</t>
-  </si>
-  <si>
-    <t>[30009,30012]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_starter_9","type":"DAMAGE","target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_starter_10","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":3,"duration":"DEFAULT"}}]</t>
-  </si>
-  <si>
-    <t>毒刃追击</t>
-  </si>
-  <si>
-    <t>施加3层中毒并攻击7点；若敌人中毒达到3层，再攻击5点并追加1层中毒。</t>
-  </si>
-  <si>
-    <t>[30009,30011]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_81","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":3,"duration":"DEFAULT"}},{"id":"e_card_82","type":"DAMAGE","target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_86","type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.poison","cmp":"&gt;=","rhs":3}]},"children":[{"id":"e_card_83","type":"DAMAGE","target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_rebalance_14","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":1,"duration":"DEFAULT"}}],"elseEffects":[{"id":"e_card_85","type":"BLOCK","target":"SELF","params":{"amount":4}}]}]</t>
-  </si>
-  <si>
-    <t>雾隐反制</t>
-  </si>
-  <si>
-    <t>获得8点格挡；本场战斗受到伤害时再次获得3点格挡、回复3点并反击4点。</t>
-  </si>
-  <si>
-    <t>[30010,30011,30010]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_87","type":"BLOCK","target":"SELF","params":{"amount":8}},{"id":"e_card_91","type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_rebalance_15","type":"BLOCK","target":"SELF","params":{"amount":3}},{"id":"e_card_89","type":"HEAL","target":"SELF","params":{"amount":3}},{"id":"e_card_90","type":"DAMAGE","target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]}]</t>
-  </si>
-  <si>
-    <t>投羽连击</t>
-  </si>
-  <si>
-    <t>连续攻击3次，每次3点；施加2层虚弱，随后获得5点格挡。</t>
-  </si>
-  <si>
-    <t>[30011,30009,30011]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_93","type":"REPEAT","target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_92","type":"DAMAGE","target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]},{"id":"e_card_94","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"WEAK","stacks":2,"duration":"DEFAULT"}},{"id":"e_rebalance_16","type":"BLOCK","target":"SELF","params":{"amount":5}}]</t>
-  </si>
-  <si>
-    <t>偷天换日</t>
-  </si>
-  <si>
-    <t>选择盗财、制敌或休整：分别获得金币与格挡、施毒并攻击、净化并回复。</t>
-  </si>
-  <si>
-    <t>[30012,30009,30010,30011]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_105","type":"CHOOSE_ONE","target":"SELF","params":{"maxChoices":1,"showCount":3},"children":[{"id":"e_card_98","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_card_96","type":"GAIN_GOLD","target":"SELF","params":{"amount":25}},{"id":"e_rebalance_17","type":"BLOCK","target":"SELF","params":{"amount":6}}]},{"id":"e_card_101","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_card_99","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":4,"duration":"DEFAULT"}},{"id":"e_card_100","type":"DAMAGE","target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]},{"id":"e_card_104","type":"SEQUENCE","target":"SELF","params":{},"children":[{"id":"e_card_102","type":"CLEANSE","target":"SELF","params":{"filter":{"kind":"DEBUFF"}}},{"id":"e_card_103","type":"HEAL","target":"SELF","params":{"amount":12}}]}]}]</t>
-  </si>
-  <si>
-    <t>钱袋伏击</t>
-  </si>
-  <si>
-    <t>获得15金币并攻击10点；若自身金币达到30，再施加易伤并回复5点，否则获得8点格挡。</t>
-  </si>
-  <si>
-    <t>[30012,30009,30012,30010]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_106","type":"GAIN_GOLD","target":"SELF","params":{"amount":15}},{"id":"e_card_107","type":"DAMAGE","target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}},{"id":"e_card_111","type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.gold","cmp":"&gt;=","rhs":30}]},"children":[{"id":"e_card_108","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"VULNERABLE","stacks":2,"duration":"DEFAULT"}},{"id":"e_rebalance_18","type":"HEAL","target":"SELF","params":{"amount":5}}],"elseEffects":[{"id":"e_card_110","type":"BLOCK","target":"SELF","params":{"amount":8}}]}]</t>
-  </si>
-  <si>
-    <t>游侠终咒</t>
-  </si>
-  <si>
-    <t>施加5层中毒；本场战斗每回合结束追加4点伤害，下回合回复6点并获得8点格挡。</t>
-  </si>
-  <si>
-    <t>[30009,30010,30011,30012]</t>
-  </si>
-  <si>
-    <t>[{"id":"e_card_112","type":"APPLY_STATUS","target":"ENEMY","params":{"status":"POISON","stacks":5,"duration":"DEFAULT"}},{"id":"e_card_114","type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_113","type":"DAMAGE","target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}}]},{"id":"e_card_117","type":"SCHEDULE","target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_115","type":"HEAL","target":"SELF","params":{"amount":6}},{"id":"e_rebalance_19","type":"BLOCK","target":"SELF","params":{"amount":8}}]}]</t>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect60"},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect61"},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect62"}]</t>
+  </si>
+  <si>
+    <t>战斗专注</t>
+  </si>
+  <si>
+    <t>抽3张牌。
+你在本回合内不能再抽任何牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210038,"target":"SELF","params":{"count":3,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect63"},{"type":210047,"target":"SELF","params":{"kind":"LOCK_DRAW","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect64"}]</t>
+  </si>
+  <si>
+    <t>燃烧契约</t>
+  </si>
+  <si>
+    <t>消耗1张牌。
+抽2张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210027,"target":"SELF","params":{"count":1,"zone":"HAND","mode":"SELECT","filter":{}},"children":[],"elseEffects":[],"id":"warriorEffect65"},{"type":210038,"target":"SELF","params":{"count":2,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect66"}]</t>
+  </si>
+  <si>
+    <t>主宰</t>
+  </si>
+  <si>
+    <t>给予1层易伤。
+敌人身上每有一层易伤，就获得1点力量。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect67"},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":"@target.buff.200004","duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect68"}]</t>
+  </si>
+  <si>
+    <t>战鼓</t>
+  </si>
+  <si>
+    <t>抽2张牌。
+这张牌被消耗时，获得2点能量。</t>
+  </si>
+  <si>
+    <t>[{"type":210038,"target":"SELF","params":{"count":2,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect69"},{"type":210037,"target":"SELF","params":{"amount":2},"children":[],"elseEffects":[],"trigger":"ON_EXHAUSTED","id":"warriorEffect70"}]</t>
+  </si>
+  <si>
+    <t>邪眼</t>
+  </si>
+  <si>
+    <t>获得8点格挡。
+如果你在本回合消耗过卡牌，则额外获得8点格挡。</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect71"},{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@battle.exhaustedThisTurn","cmp":"&gt;","rhs":0}]},"id":"warriorEffect72"}]</t>
+  </si>
+  <si>
+    <t>跃跃欲试</t>
+  </si>
+  <si>
+    <t>你的手牌中每有一张攻击牌，就获得1点能量。
+你在本回合内
+不能再获得能量。</t>
+  </si>
+  <si>
+    <t>[30001,30001]</t>
+  </si>
+  <si>
+    <t>[{"type":210037,"target":"SELF","params":{"amount":"@battle.handAttackCount"},"children":[],"elseEffects":[],"id":"warriorEffect73"},{"type":210047,"target":"SELF","params":{"kind":"LOCK_ENERGY","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect74"}]</t>
+  </si>
+  <si>
+    <t>火焰屏障</t>
+  </si>
+  <si>
+    <t>获得12点格挡。
+你在这个回合每受到一次攻击，都会对攻击者造成4点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect75"},{"type":210010,"target":"SELF","params":{"status":200009,"stacks":4,"duration":"UNTIL_ENEMY_END"},"children":[],"elseEffects":[],"id":"warriorEffect76"}]</t>
+  </si>
+  <si>
+    <t>被遗忘的仪式</t>
+  </si>
+  <si>
+    <t>如果你在本回合消耗过卡牌，则获得3点能量。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210037,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@battle.exhaustedThisTurn","cmp":"&gt;","rhs":0}]},"id":"warriorEffect77"}]</t>
+  </si>
+  <si>
+    <t>地狱之刃</t>
+  </si>
+  <si>
+    <t>将1张随机战士攻击牌加入手牌。
+这张生成的牌在本回合首次打出时无需骰子。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210045,"target":"SELF","params":{"count":1,"type":"ATTACK","freeThisTurn":true},"children":[],"elseEffects":[],"id":"warriorEffect78"}]</t>
+  </si>
+  <si>
+    <t>狂怒</t>
+  </si>
+  <si>
+    <t>打出此牌后，你在这个回合内每打出一张攻击牌，获得3点格挡。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"TURN","limit":0,"filter":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect80"}],"elseEffects":[],"id":"warriorEffect79"}]</t>
+  </si>
+  <si>
+    <t>重振精神</t>
+  </si>
+  <si>
+    <t>消耗手牌中所有非攻击牌，每张获得5点格挡。</t>
+  </si>
+  <si>
+    <t>[{"type":210027,"target":"SELF","params":{"count":"ALL","zone":"HAND","mode":"ALL","filter":{"notType":"ATTACK"}},"children":[{"type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect82"}],"elseEffects":[],"id":"warriorEffect81"}]</t>
+  </si>
+  <si>
+    <t>挑衅</t>
+  </si>
+  <si>
+    <t>获得7点格挡。
+给予敌人1层虚弱。</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":7,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect83"},{"type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect84"}]</t>
+  </si>
+  <si>
+    <t>无惧疼痛</t>
+  </si>
+  <si>
+    <t>每当有一张牌被消耗时，获得3点格挡。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_EXHAUST","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect86"}],"elseEffects":[],"id":"warriorEffect85"}]</t>
+  </si>
+  <si>
+    <t>狱火</t>
+  </si>
+  <si>
+    <t>在你的回合开始时，失去1点生命。
+每当你在你的回合内失去生命时，对敌人造成6点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210004,"target":"SELF","params":{"amount":1,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect88"}],"elseEffects":[],"id":"warriorEffect87"},{"type":210022,"target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@battle.playerTurn","cmp":"==","rhs":1}]},"id":"warriorEffect90"}],"elseEffects":[],"id":"warriorEffect89"}]</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>获得2点力量。</t>
+  </si>
+  <si>
+    <t>[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":2,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect91"}]</t>
+  </si>
+  <si>
+    <t>杂耍</t>
+  </si>
+  <si>
+    <t>将你在每回合打出的第三张攻击牌的复制品加入你的手牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210042,"target":"SELF","params":{"source":"EVENT","pile":"HAND"},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@event.attackCount","cmp":"==","rhs":3}]},"id":"warriorEffect93"}],"elseEffects":[],"id":"warriorEffect92"}]</t>
+  </si>
+  <si>
+    <t>撕裂</t>
+  </si>
+  <si>
+    <t>每当你在你的回合失去生命值时, 获得1点力量。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@battle.playerTurn","cmp":"==","rhs":1}]},"id":"warriorEffect95"}],"elseEffects":[],"id":"warriorEffect94"}]</t>
+  </si>
+  <si>
+    <t>惊逃</t>
+  </si>
+  <si>
+    <t>回合结束时，随机打出手牌中的1张攻击牌攻击当前敌人，不消耗骰子。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210043,"target":"SELF","params":{"pile":"HAND","mode":"RANDOM_ATTACK","exhaustAfter":false},"children":[],"elseEffects":[],"id":"warriorEffect97"}],"elseEffects":[],"id":"warriorEffect96"}]</t>
+  </si>
+  <si>
+    <t>岩石铠甲</t>
+  </si>
+  <si>
+    <t>获得4层覆甲。</t>
+  </si>
+  <si>
+    <t>[{"type":210010,"target":"SELF","params":{"status":200016,"stacks":4,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect98"}]</t>
+  </si>
+  <si>
+    <t>凶恶</t>
+  </si>
+  <si>
+    <t>每当你给予易伤时，抽1张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_STATUS_APPLIED","scope":"COMBAT","limit":0,"filter":{"status":200004}},"children":[{"type":210038,"target":"SELF","params":{"count":1,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect100"}],"elseEffects":[],"id":"warriorEffect99"}]</t>
+  </si>
+  <si>
+    <t>焚烧</t>
+  </si>
+  <si>
+    <t>对敌人造成2点伤害4次。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":2,"hits":4,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect101"}]</t>
+  </si>
+  <si>
+    <t>狂宴</t>
+  </si>
+  <si>
+    <t>造成10点伤害。
+斩杀时，永久获得3点最大生命值。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect102"},{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":3,"duration":"COMBAT","persistent":true},"children":[],"elseEffects":[],"trigger":"ON_KILL_WITH_THIS_CARD","id":"warriorEffect103"}]</t>
+  </si>
+  <si>
+    <t>恶魔之焰</t>
+  </si>
+  <si>
+    <t>消耗所有手牌。
+每张被消耗的牌造成7点伤害。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210027,"target":"SELF","params":{"count":"ALL","zone":"HAND","mode":"ALL","filter":{}},"children":[],"elseEffects":[],"id":"warriorEffect104"},{"type":210001,"target":"ENEMY","params":{"amount":7,"hits":"@exhaustedCount","damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect105"}]</t>
+  </si>
+  <si>
+    <t>凌虐</t>
+  </si>
+  <si>
+    <t>造成15点伤害。
+敌人失去10点力量，直到敌人的本次行动结束后恢复。</t>
+  </si>
+  <si>
+    <t>[30002,30002,30003]</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":15,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect106"},{"type":210010,"target":"ENEMY","params":{"status":200001,"stacks":-10,"duration":"TURN"},"children":[],"elseEffects":[],"id":"warriorEffect107"}]</t>
+  </si>
+  <si>
+    <t>契约终结</t>
+  </si>
+  <si>
+    <t>如果你的消耗牌堆拥有大于等于3张牌，
+则对敌人造成17点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":17,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@battle.exhaustCount","cmp":"&gt;=","rhs":3}]},"id":"warriorEffect108"}]</t>
+  </si>
+  <si>
+    <t>扯碎</t>
+  </si>
+  <si>
+    <t>造成5点伤害。
+在本场战斗中，你每失去过一次生命值，这张牌就额外造成一次伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":5,"hits":"1+@battle.hpLossCount","damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect109"}]</t>
+  </si>
+  <si>
+    <t>痛殴</t>
+  </si>
+  <si>
+    <t>造成4点伤害两次。
+消耗你的手牌中随机一张攻击牌，并将它的伤害添加给这张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":4,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect110"},{"type":210027,"target":"SELF","params":{"count":1,"zone":"HAND","mode":"RANDOM","filter":{"type":"ATTACK"}},"children":[{"type":210046,"target":"SELF","params":{"amount":"@exhaustedDamage"},"children":[],"elseEffects":[],"id":"warriorEffect112"}],"elseEffects":[],"id":"warriorEffect111"}]</t>
+  </si>
+  <si>
+    <t>烙印</t>
+  </si>
+  <si>
+    <t>失去1点生命。
+消耗1张牌。
+获得1点力量。</t>
+  </si>
+  <si>
+    <t>[{"type":210004,"target":"SELF","params":{"amount":1,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect113"},{"type":210027,"target":"SELF","params":{"count":1,"zone":"HAND","mode":"SELECT","filter":{}},"children":[],"elseEffects":[],"id":"warriorEffect114"},{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect115"}]</t>
+  </si>
+  <si>
+    <t>岿然不动</t>
+  </si>
+  <si>
+    <t>获得30点格挡。
+消耗。</t>
+  </si>
+  <si>
+    <t>[30002,30002]</t>
+  </si>
+  <si>
+    <t>[{"type":210002,"target":"SELF","params":{"amount":30,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect116"}]</t>
+  </si>
+  <si>
+    <t>时候未到</t>
+  </si>
+  <si>
+    <t>回复10点生命。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210003,"target":"SELF","params":{"amount":10},"children":[],"elseEffects":[],"id":"warriorEffect117"}]</t>
+  </si>
+  <si>
+    <t>祭品</t>
+  </si>
+  <si>
+    <t>失去6点生命。
+获得2点能量。
+抽3张牌。
+消耗。</t>
+  </si>
+  <si>
+    <t>[{"type":210004,"target":"SELF","params":{"amount":6,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect118"},{"type":210037,"target":"SELF","params":{"amount":2},"children":[],"elseEffects":[],"id":"warriorEffect119"},{"type":210038,"target":"SELF","params":{"count":3,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect120"}]</t>
+  </si>
+  <si>
+    <t>连环拳</t>
+  </si>
+  <si>
+    <t>本回合你打出的下一张攻击牌，其效果额外结算1次，不重复消耗骰子。</t>
+  </si>
+  <si>
+    <t>[{"type":210047,"target":"SELF","params":{"kind":"NEXT_ATTACK_REPEAT","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect121"}]</t>
+  </si>
+  <si>
+    <t>原始力量</t>
+  </si>
+  <si>
+    <t>将手牌中的所有攻击牌变化为巨石。
+巨石：需要1颗斧头骰子，造成16点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210044,"target":"SELF","params":{"cardId":20112,"type":"ATTACK"},"children":[],"elseEffects":[],"id":"warriorEffect122"}]</t>
+  </si>
+  <si>
+    <t>添柴</t>
+  </si>
+  <si>
+    <t>消耗所有手牌。
+每消耗1张牌，将1张随机战士牌加入手牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210027,"target":"SELF","params":{"count":"ALL","zone":"HAND","mode":"ALL","filter":{}},"children":[],"elseEffects":[],"id":"warriorEffect123"},{"type":210045,"target":"SELF","params":{"count":"@exhaustedCount","type":"ALL","freeThisTurn":false},"children":[],"elseEffects":[],"id":"warriorEffect124"}]</t>
+  </si>
+  <si>
+    <t>壁垒</t>
+  </si>
+  <si>
+    <t>格挡不再在你的回合开始时消失。</t>
+  </si>
+  <si>
+    <t>[30002,30002,30002]</t>
+  </si>
+  <si>
+    <t>[{"type":210010,"target":"SELF","params":{"status":200012,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect125"}]</t>
+  </si>
+  <si>
+    <t>绯红披风</t>
+  </si>
+  <si>
+    <t>在你的回合开始时，失去1点生命并获得8点格挡。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210004,"target":"SELF","params":{"amount":1,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect127"},{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect128"}],"elseEffects":[],"id":"warriorEffect126"}]</t>
+  </si>
+  <si>
+    <t>残酷</t>
+  </si>
+  <si>
+    <t>有易伤状态的敌人额外受到25%的伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210047,"target":"SELF","params":{"kind":"VULNERABLE_BONUS","amount":0.25},"children":[],"elseEffects":[],"id":"warriorEffect129"}]</t>
+  </si>
+  <si>
+    <t>黑暗之拥</t>
+  </si>
+  <si>
+    <t>每当有一张牌被消耗时，
+抽1张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_EXHAUST","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect131"}],"elseEffects":[],"id":"warriorEffect130"}]</t>
+  </si>
+  <si>
+    <t>恶魔形态</t>
+  </si>
+  <si>
+    <t>在你的回合开始时，获得2点力量。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":2,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect133"}],"elseEffects":[],"id":"warriorEffect132"}]</t>
+  </si>
+  <si>
+    <t>地狱狂徒</t>
+  </si>
+  <si>
+    <t>每当你抽到名字中含有“打击”的牌时，无需骰子对当前敌人打出这张牌。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_CARD_DRAWN","scope":"COMBAT","limit":0,"filter":{"strike":true}},"children":[{"type":210043,"target":"SELF","params":{"pile":"HAND","mode":"EVENT","exhaustAfter":false},"children":[],"elseEffects":[],"id":"warriorEffect135"}],"elseEffects":[],"id":"warriorEffect134"}]</t>
+  </si>
+  <si>
+    <t>势不可当</t>
+  </si>
+  <si>
+    <t>每当你获得格挡时，对敌人造成6点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_GAINED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect137"}],"elseEffects":[],"id":"warriorEffect136"}]</t>
+  </si>
+  <si>
+    <t>薪火之源</t>
+  </si>
+  <si>
+    <t>在回合开始时，获得1点能量。</t>
+  </si>
+  <si>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[],"id":"warriorEffect139"}],"elseEffects":[],"id":"warriorEffect138"}]</t>
+  </si>
+  <si>
+    <t>坚定不移</t>
+  </si>
+  <si>
+    <t>翻倍你每回合第一次从卡牌中获得的格挡。</t>
+  </si>
+  <si>
+    <t>[{"type":210047,"target":"SELF","params":{"kind":"FIRST_BLOCK_DOUBLE","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect140"}]</t>
+  </si>
+  <si>
+    <t>破击</t>
+  </si>
+  <si>
+    <t>造成20点伤害。
+给予5层易伤。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":20,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect141"},{"type":210010,"target":"ENEMY","params":{"status":200004,"stacks":5,"duration":"DEFAULT"},"children":[],"elseEffects":[],"id":"warriorEffect142"}]</t>
+  </si>
+  <si>
+    <t>{"special":true}</t>
+  </si>
+  <si>
+    <t>腐化</t>
+  </si>
+  <si>
+    <t>本场战斗中，技能牌无需骰子。
+每次打出技能牌后，将其消耗。</t>
+  </si>
+  <si>
+    <t>[30001,30001,30001]</t>
+  </si>
+  <si>
+    <t>[{"type":210047,"target":"SELF","params":{"kind":"SKILL_FREE_EXHAUST","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect143"}]</t>
+  </si>
+  <si>
+    <t>巨石</t>
+  </si>
+  <si>
+    <t>造成16点伤害。</t>
+  </si>
+  <si>
+    <t>[{"type":210001,"target":"ENEMY","params":{"amount":16,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect144"}]</t>
+  </si>
+  <si>
+    <t>{"generated":true}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -502,25 +1591,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -774,17 +2149,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L106"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.5916666666667" customWidth="1"/>
-    <col min="3" max="3" width="13.3583333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.0916666666667" customWidth="1"/>
+    <col min="3" max="3" width="113.833333333333" customWidth="1"/>
+    <col min="4" max="4" width="38.9416666666667" customWidth="1"/>
     <col min="8" max="8" width="24.5166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -822,7 +2198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -860,7 +2236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -898,7 +2274,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" customHeight="1" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -936,7 +2312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" customHeight="1" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -974,9 +2350,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" customHeight="1" spans="1:12">
       <c r="A6" s="1">
-        <v>20001</v>
+        <v>20011</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -994,12 +2370,10 @@
         <v>50</v>
       </c>
       <c r="G6" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_1","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
       </c>
       <c r="I6" t="s">
         <v>34</v>
@@ -1011,9 +2385,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" customHeight="1" spans="1:12">
       <c r="A7" s="1">
-        <v>20002</v>
+        <v>20012</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>37</v>
@@ -1031,12 +2405,10 @@
         <v>50</v>
       </c>
       <c r="G7" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[{"id":"e_starter_1","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
       </c>
       <c r="I7" t="s">
         <v>41</v>
@@ -1048,9 +2420,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" customHeight="1" spans="1:12">
       <c r="A8" s="1">
-        <v>20003</v>
+        <v>20013</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>43</v>
@@ -1068,12 +2440,10 @@
         <v>50</v>
       </c>
       <c r="G8" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[{"id":"e_starter_2","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
       </c>
       <c r="I8" t="s">
         <v>34</v>
@@ -1085,9 +2455,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" customHeight="1" spans="1:12">
       <c r="A9" s="1">
-        <v>20004</v>
+        <v>20014</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>47</v>
@@ -1105,12 +2475,10 @@
         <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[{"id":"e_starter_3","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_4","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
       </c>
       <c r="I9" t="s">
         <v>34</v>
@@ -1122,9 +2490,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" customHeight="1" spans="1:12">
       <c r="A10" s="1">
-        <v>20005</v>
+        <v>20015</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
@@ -1142,12 +2510,10 @@
         <v>100</v>
       </c>
       <c r="G10" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_6","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_10","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.block","cmp":"&gt;=","rhs":8}]},"children":[{"id":"e_card_7","type":210001,"target":"ENEMY","params":{"amount":9,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_8","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_9","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H10" t="s">
+        <v>54</v>
       </c>
       <c r="I10" t="s">
         <v>34</v>
@@ -1159,9 +2525,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" customHeight="1" spans="1:12">
       <c r="A11" s="1">
-        <v>20006</v>
+        <v>20016</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>55</v>
@@ -1179,35 +2545,33 @@
         <v>100</v>
       </c>
       <c r="G11" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_11","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_14","type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_12","type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_13","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H11" t="s">
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="A12" s="1">
+        <v>20017</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>20007</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -1216,26 +2580,24 @@
         <v>100</v>
       </c>
       <c r="G12" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_16","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_15","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_17","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_2","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H12" t="s">
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="L12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" customHeight="1" spans="1:12">
       <c r="A13" s="1">
-        <v>20008</v>
+        <v>20018</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>64</v>
@@ -1253,12 +2615,10 @@
         <v>180</v>
       </c>
       <c r="G13" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_22","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;=","rhs":50}]},"children":[{"id":"e_card_19","type":210003,"target":"SELF","params":{"amount":8},"children":[],"elseEffects":[]},{"id":"e_card_20","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_21","type":210002,"target":"SELF","params":{"amount":12,"scale":true},"children":[],"elseEffects":[]}]},{"id":"e_card_25","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_23","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]},{"id":"e_rebalance_3","type":210003,"target":"SELF","params":{"amount":4},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H13" t="s">
+        <v>67</v>
       </c>
       <c r="I13" t="s">
         <v>41</v>
@@ -1270,9 +2630,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" customHeight="1" spans="1:12">
       <c r="A14" s="1">
-        <v>20009</v>
+        <v>20019</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>68</v>
@@ -1290,26 +2650,24 @@
         <v>180</v>
       </c>
       <c r="G14" s="1">
-        <v>10001</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_26","type":210015,"target":"SELF","params":{"stat":200001,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_27","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_30","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_28","type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_29","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
       </c>
       <c r="I14" t="s">
         <v>41</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" customHeight="1" spans="1:12">
       <c r="A15">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="B15" t="s">
         <v>72</v>
@@ -1327,26 +2685,24 @@
         <v>180</v>
       </c>
       <c r="G15">
-        <v>10001</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_40","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":3},"children":[{"id":"e_card_33","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_31","type":210002,"target":"SELF","params":{"amount":16,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_32","type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_36","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_34","type":210001,"target":"ENEMY","params":{"amount":12,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_35","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_39","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_37","type":210003,"target":"SELF","params":{"amount":10},"children":[],"elseEffects":[]},{"id":"e_rebalance_4","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10002</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J15" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="L15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" customHeight="1" spans="1:12">
       <c r="A16">
-        <v>20011</v>
+        <v>20021</v>
       </c>
       <c r="B16" t="s">
         <v>76</v>
@@ -1364,12 +2720,10 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>10002</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_41","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H16" t="s">
+        <v>78</v>
       </c>
       <c r="I16" t="s">
         <v>34</v>
@@ -1381,9 +2735,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" customHeight="1" spans="1:12">
       <c r="A17">
-        <v>20012</v>
+        <v>20022</v>
       </c>
       <c r="B17" t="s">
         <v>79</v>
@@ -1401,12 +2755,10 @@
         <v>50</v>
       </c>
       <c r="G17">
-        <v>10002</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_42","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H17" t="s">
+        <v>81</v>
       </c>
       <c r="I17" t="s">
         <v>41</v>
@@ -1418,9 +2770,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" customHeight="1" spans="1:12">
       <c r="A18">
-        <v>20013</v>
+        <v>20023</v>
       </c>
       <c r="B18" t="s">
         <v>82</v>
@@ -1438,12 +2790,10 @@
         <v>50</v>
       </c>
       <c r="G18">
-        <v>10002</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_43","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H18" t="s">
+        <v>84</v>
       </c>
       <c r="I18" t="s">
         <v>34</v>
@@ -1455,9 +2805,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" customHeight="1" spans="1:12">
       <c r="A19">
-        <v>20014</v>
+        <v>20024</v>
       </c>
       <c r="B19" t="s">
         <v>85</v>
@@ -1475,12 +2825,10 @@
         <v>50</v>
       </c>
       <c r="G19">
-        <v>10002</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[{"id":"e_starter_5","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_6","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H19" t="s">
+        <v>88</v>
       </c>
       <c r="I19" t="s">
         <v>34</v>
@@ -1492,9 +2840,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" customHeight="1" spans="1:12">
       <c r="A20">
-        <v>20015</v>
+        <v>20025</v>
       </c>
       <c r="B20" t="s">
         <v>89</v>
@@ -1512,12 +2860,10 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>10002</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_46","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_45","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_rebalance_6","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_48","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H20" t="s">
+        <v>92</v>
       </c>
       <c r="I20" t="s">
         <v>34</v>
@@ -1529,9 +2875,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" customHeight="1" spans="1:12">
       <c r="A21">
-        <v>20016</v>
+        <v>20026</v>
       </c>
       <c r="B21" t="s">
         <v>93</v>
@@ -1549,26 +2895,24 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>10002</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_49","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_50","type":210026,"target":"SELF","params":{"count":1,"mode":"SELECT","filter":{}},"children":[],"elseEffects":[]},{"id":"e_card_53","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":30}]},"children":[{"id":"e_card_51","type":210001,"target":"ENEMY","params":{"amount":5,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_rebalance_7","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H21" t="s">
+        <v>96</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J21" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="L21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" customHeight="1" spans="1:12">
       <c r="A22">
-        <v>20017</v>
+        <v>20027</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
@@ -1586,26 +2930,24 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>10002</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[{"id":"e_rebalance_8","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_57","type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_55","type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_56","type":210002,"target":"SELF","params":{"amount":2,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H22" t="s">
+        <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J22" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L22" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" customHeight="1" spans="1:12">
       <c r="A23">
-        <v>20018</v>
+        <v>20028</v>
       </c>
       <c r="B23" t="s">
         <v>101</v>
@@ -1623,12 +2965,10 @@
         <v>180</v>
       </c>
       <c r="G23">
-        <v>10002</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_65","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":2},"children":[{"id":"e_card_61","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_59","type":210021,"target":"ENEMY","params":{"count":4,"maxIterations":10},"children":[{"id":"e_card_58","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_60","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_64","type":210020,"target":"SELF","params":{},"children":[{"id":"e_rebalance_9","type":210015,"target":"SELF","params":{"stat":200002,"amount":2,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_63","type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H23" t="s">
+        <v>104</v>
       </c>
       <c r="I23" t="s">
         <v>41</v>
@@ -1640,9 +2980,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" customHeight="1" spans="1:12">
       <c r="A24">
-        <v>20019</v>
+        <v>20029</v>
       </c>
       <c r="B24" t="s">
         <v>105</v>
@@ -1660,26 +3000,24 @@
         <v>180</v>
       </c>
       <c r="G24">
-        <v>10002</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_66","type":210002,"target":"SELF","params":{"amount":10,"scale":true},"children":[],"elseEffects":[]},{"id":"e_rebalance_10","type":210015,"target":"SELF","params":{"stat":200002,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_70","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_rebalance_11","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_69","type":210001,"target":"ENEMY","params":{"amount":6,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H24" t="s">
+        <v>108</v>
       </c>
       <c r="I24" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J24" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="L24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" customHeight="1" spans="1:12">
       <c r="A25">
-        <v>20020</v>
+        <v>20030</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
@@ -1697,35 +3035,33 @@
         <v>180</v>
       </c>
       <c r="G25">
-        <v>10002</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_76","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.hp","cmp":"&lt;=","rhs":18}]},"children":[{"id":"e_card_71","type":210005,"target":"ENEMY","params":{"threshold":18},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_73","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_72","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_74","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_12","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}]}]</t>
-        </is>
+        <v>10003</v>
+      </c>
+      <c r="H25" t="s">
+        <v>112</v>
       </c>
       <c r="I25" t="s">
         <v>34</v>
       </c>
       <c r="J25" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="L25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" customHeight="1" spans="1:12">
       <c r="A26">
-        <v>20021</v>
+        <v>20031</v>
       </c>
       <c r="B26" t="s">
         <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1734,12 +3070,10 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>10003</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_77","type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10001</v>
+      </c>
+      <c r="H26" t="s">
+        <v>116</v>
       </c>
       <c r="I26" t="s">
         <v>34</v>
@@ -1748,21 +3082,21 @@
         <v>35</v>
       </c>
       <c r="L26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
       <c r="A27">
-        <v>20022</v>
+        <v>20032</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -1771,35 +3105,33 @@
         <v>50</v>
       </c>
       <c r="G27">
-        <v>10003</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[{"id":"e_starter_8","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10001</v>
+      </c>
+      <c r="H27" t="s">
+        <v>120</v>
       </c>
       <c r="I27" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="L27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
       <c r="A28">
-        <v>20023</v>
+        <v>20033</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1808,35 +3140,33 @@
         <v>50</v>
       </c>
       <c r="G28">
-        <v>10003</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[{"id":"e_starter_7","type":210001,"target":"ENEMY","params":{"amount":3,"hits":2,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10001</v>
+      </c>
+      <c r="H28" t="s">
+        <v>123</v>
       </c>
       <c r="I28" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J28" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:12">
       <c r="A29">
-        <v>20024</v>
+        <v>20034</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1845,12 +3175,10 @@
         <v>50</v>
       </c>
       <c r="G29">
-        <v>10003</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[{"id":"e_starter_9","type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_starter_10","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]}]</t>
-        </is>
+        <v>10001</v>
+      </c>
+      <c r="H29" t="s">
+        <v>127</v>
       </c>
       <c r="I29" t="s">
         <v>34</v>
@@ -1862,32 +3190,30 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" customHeight="1" spans="1:12">
       <c r="A30">
-        <v>20025</v>
+        <v>20035</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>10003</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_81","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":3,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_82","type":210001,"target":"ENEMY","params":{"amount":7,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_86","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@target.buff.200006","cmp":"&gt;=","rhs":3}]},"children":[{"id":"e_card_83","type":210001,"target":"ENEMY","params":{"amount":5,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_rebalance_14","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":1,"duration":"DEFAULT"},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_85","type":210002,"target":"SELF","params":{"amount":4,"scale":true},"children":[],"elseEffects":[]}]}]</t>
-        </is>
+        <v>10001</v>
+      </c>
+      <c r="H30" t="s">
+        <v>130</v>
       </c>
       <c r="I30" t="s">
         <v>34</v>
@@ -1899,46 +3225,44 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" customHeight="1" spans="1:12">
       <c r="A31">
-        <v>20026</v>
+        <v>20036</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G31">
-        <v>10003</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_87","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_91","type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_rebalance_15","type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_89","type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]},{"id":"e_card_90","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+        <v>10001</v>
+      </c>
+      <c r="H31" t="s">
+        <v>133</v>
       </c>
       <c r="I31" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J31" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L31" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" customHeight="1" spans="1:12">
       <c r="A32">
-        <v>20027</v>
+        <v>20037</v>
       </c>
       <c r="B32" t="s">
         <v>134</v>
@@ -1947,21 +3271,19 @@
         <v>135</v>
       </c>
       <c r="D32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>50</v>
+      </c>
+      <c r="G32">
+        <v>10001</v>
+      </c>
+      <c r="H32" t="s">
         <v>136</v>
-      </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
-      <c r="F32">
-        <v>100</v>
-      </c>
-      <c r="G32">
-        <v>10003</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_93","type":210021,"target":"ENEMY","params":{"count":3,"maxIterations":10},"children":[{"id":"e_card_92","type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_94","type":210010,"target":"ENEMY","params":{"status":200003,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_16","type":210002,"target":"SELF","params":{"amount":5,"scale":true},"children":[],"elseEffects":[]}]</t>
-        </is>
       </c>
       <c r="I32" t="s">
         <v>34</v>
@@ -1973,69 +3295,65 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" customHeight="1" spans="1:12">
       <c r="A33">
-        <v>20028</v>
+        <v>20038</v>
       </c>
       <c r="B33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" t="s">
         <v>138</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>139</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>50</v>
+      </c>
+      <c r="G33">
+        <v>10001</v>
+      </c>
+      <c r="H33" t="s">
         <v>140</v>
       </c>
-      <c r="E33">
-        <v>3</v>
-      </c>
-      <c r="F33">
-        <v>180</v>
-      </c>
-      <c r="G33">
-        <v>10003</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_105","type":210024,"target":"SELF","params":{"maxChoices":1,"showCount":3},"children":[{"id":"e_card_98","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_96","type":210031,"target":"SELF","params":{"amount":25},"children":[],"elseEffects":[]},{"id":"e_rebalance_17","type":210002,"target":"SELF","params":{"amount":6,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_101","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_99","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":4,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_100","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_104","type":210020,"target":"SELF","params":{},"children":[{"id":"e_card_102","type":210014,"target":"SELF","params":{"filter":{"kind":"DEBUFF"}},"children":[],"elseEffects":[]},{"id":"e_card_103","type":210003,"target":"SELF","params":{"amount":12},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
-      </c>
       <c r="I33" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J33" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="L33" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" customHeight="1" spans="1:12">
       <c r="A34">
-        <v>20029</v>
+        <v>20039</v>
       </c>
       <c r="B34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" t="s">
         <v>142</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+      <c r="G34">
+        <v>10001</v>
+      </c>
+      <c r="H34" t="s">
         <v>143</v>
-      </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34">
-        <v>3</v>
-      </c>
-      <c r="F34">
-        <v>180</v>
-      </c>
-      <c r="G34">
-        <v>10003</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_106","type":210031,"target":"SELF","params":{"amount":15},"children":[],"elseEffects":[]},{"id":"e_card_107","type":210001,"target":"ENEMY","params":{"amount":10,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_111","type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.gold","cmp":"&gt;=","rhs":30}]},"children":[{"id":"e_card_108","type":210010,"target":"ENEMY","params":{"status":200004,"stacks":2,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_rebalance_18","type":210003,"target":"SELF","params":{"amount":5},"children":[],"elseEffects":[]}],"elseEffects":[{"id":"e_card_110","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}]}]</t>
-        </is>
       </c>
       <c r="I34" t="s">
         <v>34</v>
@@ -2047,45 +3365,2529 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" customHeight="1" spans="1:12">
       <c r="A35">
-        <v>20030</v>
+        <v>20040</v>
       </c>
       <c r="B35" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>50</v>
+      </c>
+      <c r="G35">
+        <v>10001</v>
+      </c>
+      <c r="H35" t="s">
         <v>146</v>
-      </c>
-      <c r="C35" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35">
-        <v>3</v>
-      </c>
-      <c r="F35">
-        <v>180</v>
-      </c>
-      <c r="G35">
-        <v>10003</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[{"id":"e_card_112","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":5,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_114","type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_113","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_117","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_115","type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]},{"id":"e_rebalance_19","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
       </c>
       <c r="I35" t="s">
         <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L35" t="s">
-        <v>36</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:12">
+      <c r="A36">
+        <v>20041</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>50</v>
+      </c>
+      <c r="G36">
+        <v>10001</v>
+      </c>
+      <c r="H36" t="s">
+        <v>150</v>
+      </c>
+      <c r="I36" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:12">
+      <c r="A37">
+        <v>20042</v>
+      </c>
+      <c r="B37" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="G37">
+        <v>10001</v>
+      </c>
+      <c r="H37" t="s">
+        <v>153</v>
+      </c>
+      <c r="I37" t="s">
+        <v>34</v>
+      </c>
+      <c r="J37" t="s">
+        <v>35</v>
+      </c>
+      <c r="L37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:12">
+      <c r="A38">
+        <v>20043</v>
+      </c>
+      <c r="B38" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" t="s">
+        <v>155</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>50</v>
+      </c>
+      <c r="G38">
+        <v>10001</v>
+      </c>
+      <c r="H38" t="s">
+        <v>156</v>
+      </c>
+      <c r="I38" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" t="s">
+        <v>35</v>
+      </c>
+      <c r="L38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
+      <c r="A39">
+        <v>20044</v>
+      </c>
+      <c r="B39" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>50</v>
+      </c>
+      <c r="G39">
+        <v>10001</v>
+      </c>
+      <c r="H39" t="s">
+        <v>159</v>
+      </c>
+      <c r="I39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:12">
+      <c r="A40">
+        <v>20045</v>
+      </c>
+      <c r="B40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C40" t="s">
+        <v>161</v>
+      </c>
+      <c r="D40" t="s">
+        <v>122</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>10001</v>
+      </c>
+      <c r="H40" t="s">
+        <v>162</v>
+      </c>
+      <c r="I40" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" t="s">
+        <v>35</v>
+      </c>
+      <c r="L40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
+      <c r="A41">
+        <v>20046</v>
+      </c>
+      <c r="B41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>50</v>
+      </c>
+      <c r="G41">
+        <v>10001</v>
+      </c>
+      <c r="H41" t="s">
+        <v>165</v>
+      </c>
+      <c r="I41" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" t="s">
+        <v>35</v>
+      </c>
+      <c r="L41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:12">
+      <c r="A42">
+        <v>20048</v>
+      </c>
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>50</v>
+      </c>
+      <c r="G42">
+        <v>10001</v>
+      </c>
+      <c r="H42" t="s">
+        <v>168</v>
+      </c>
+      <c r="I42" t="s">
+        <v>41</v>
+      </c>
+      <c r="J42" t="s">
+        <v>42</v>
+      </c>
+      <c r="L42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:12">
+      <c r="A43">
+        <v>20049</v>
+      </c>
+      <c r="B43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" t="s">
+        <v>170</v>
+      </c>
+      <c r="D43" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>50</v>
+      </c>
+      <c r="G43">
+        <v>10001</v>
+      </c>
+      <c r="H43" t="s">
+        <v>171</v>
+      </c>
+      <c r="I43" t="s">
+        <v>41</v>
+      </c>
+      <c r="J43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:12">
+      <c r="A44">
+        <v>20050</v>
+      </c>
+      <c r="B44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>50</v>
+      </c>
+      <c r="G44">
+        <v>10001</v>
+      </c>
+      <c r="H44" t="s">
+        <v>174</v>
+      </c>
+      <c r="I44" t="s">
+        <v>41</v>
+      </c>
+      <c r="J44" t="s">
+        <v>42</v>
+      </c>
+      <c r="L44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:12">
+      <c r="A45">
+        <v>20051</v>
+      </c>
+      <c r="B45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>50</v>
+      </c>
+      <c r="G45">
+        <v>10001</v>
+      </c>
+      <c r="H45" t="s">
+        <v>177</v>
+      </c>
+      <c r="I45" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" t="s">
+        <v>42</v>
+      </c>
+      <c r="L45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:12">
+      <c r="A46">
+        <v>20052</v>
+      </c>
+      <c r="B46" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D46" t="s">
+        <v>119</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>50</v>
+      </c>
+      <c r="G46">
+        <v>10001</v>
+      </c>
+      <c r="H46" t="s">
+        <v>180</v>
+      </c>
+      <c r="I46" t="s">
+        <v>34</v>
+      </c>
+      <c r="J46" t="s">
+        <v>42</v>
+      </c>
+      <c r="L46" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:12">
+      <c r="A47">
+        <v>20053</v>
+      </c>
+      <c r="B47" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" t="s">
+        <v>122</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="G47">
+        <v>10001</v>
+      </c>
+      <c r="H47" t="s">
+        <v>183</v>
+      </c>
+      <c r="I47" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" t="s">
+        <v>42</v>
+      </c>
+      <c r="L47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:12">
+      <c r="A48">
+        <v>20054</v>
+      </c>
+      <c r="B48" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" t="s">
+        <v>185</v>
+      </c>
+      <c r="D48" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>50</v>
+      </c>
+      <c r="G48">
+        <v>10001</v>
+      </c>
+      <c r="H48" t="s">
+        <v>186</v>
+      </c>
+      <c r="I48" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" t="s">
+        <v>35</v>
+      </c>
+      <c r="L48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:12">
+      <c r="A49">
+        <v>20055</v>
+      </c>
+      <c r="B49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C49" t="s">
+        <v>188</v>
+      </c>
+      <c r="D49" t="s">
+        <v>189</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>50</v>
+      </c>
+      <c r="G49">
+        <v>10001</v>
+      </c>
+      <c r="H49" t="s">
+        <v>190</v>
+      </c>
+      <c r="I49" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" t="s">
+        <v>35</v>
+      </c>
+      <c r="L49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:12">
+      <c r="A50">
+        <v>20056</v>
+      </c>
+      <c r="B50" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>50</v>
+      </c>
+      <c r="G50">
+        <v>10001</v>
+      </c>
+      <c r="H50" t="s">
+        <v>193</v>
+      </c>
+      <c r="I50" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" t="s">
+        <v>35</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:12">
+      <c r="A51">
+        <v>20057</v>
+      </c>
+      <c r="B51" t="s">
+        <v>194</v>
+      </c>
+      <c r="C51" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>50</v>
+      </c>
+      <c r="G51">
+        <v>10001</v>
+      </c>
+      <c r="H51" t="s">
+        <v>196</v>
+      </c>
+      <c r="I51" t="s">
+        <v>34</v>
+      </c>
+      <c r="J51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:12">
+      <c r="A52">
+        <v>20058</v>
+      </c>
+      <c r="B52" t="s">
+        <v>197</v>
+      </c>
+      <c r="C52" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>50</v>
+      </c>
+      <c r="G52">
+        <v>10001</v>
+      </c>
+      <c r="H52" t="s">
+        <v>199</v>
+      </c>
+      <c r="I52" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" t="s">
+        <v>35</v>
+      </c>
+      <c r="L52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:12">
+      <c r="A53">
+        <v>20059</v>
+      </c>
+      <c r="B53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>10001</v>
+      </c>
+      <c r="H53" t="s">
+        <v>202</v>
+      </c>
+      <c r="I53" t="s">
+        <v>34</v>
+      </c>
+      <c r="J53" t="s">
+        <v>35</v>
+      </c>
+      <c r="L53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:12">
+      <c r="A54">
+        <v>20060</v>
+      </c>
+      <c r="B54" t="s">
+        <v>203</v>
+      </c>
+      <c r="C54" t="s">
+        <v>204</v>
+      </c>
+      <c r="D54" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>50</v>
+      </c>
+      <c r="G54">
+        <v>10001</v>
+      </c>
+      <c r="H54" t="s">
+        <v>205</v>
+      </c>
+      <c r="I54" t="s">
+        <v>34</v>
+      </c>
+      <c r="J54" t="s">
+        <v>35</v>
+      </c>
+      <c r="L54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:12">
+      <c r="A55">
+        <v>20061</v>
+      </c>
+      <c r="B55" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" t="s">
+        <v>207</v>
+      </c>
+      <c r="D55" t="s">
+        <v>139</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>50</v>
+      </c>
+      <c r="G55">
+        <v>10001</v>
+      </c>
+      <c r="H55" t="s">
+        <v>208</v>
+      </c>
+      <c r="I55" t="s">
+        <v>34</v>
+      </c>
+      <c r="J55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:12">
+      <c r="A56">
+        <v>20062</v>
+      </c>
+      <c r="B56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56" t="s">
+        <v>210</v>
+      </c>
+      <c r="D56" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>50</v>
+      </c>
+      <c r="G56">
+        <v>10001</v>
+      </c>
+      <c r="H56" t="s">
+        <v>211</v>
+      </c>
+      <c r="I56" t="s">
+        <v>34</v>
+      </c>
+      <c r="J56" t="s">
+        <v>35</v>
+      </c>
+      <c r="L56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:12">
+      <c r="A57">
+        <v>20063</v>
+      </c>
+      <c r="B57" t="s">
+        <v>212</v>
+      </c>
+      <c r="C57" t="s">
+        <v>213</v>
+      </c>
+      <c r="D57" t="s">
+        <v>126</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>50</v>
+      </c>
+      <c r="G57">
+        <v>10001</v>
+      </c>
+      <c r="H57" t="s">
+        <v>214</v>
+      </c>
+      <c r="I57" t="s">
+        <v>34</v>
+      </c>
+      <c r="J57" t="s">
+        <v>35</v>
+      </c>
+      <c r="L57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:12">
+      <c r="A58">
+        <v>20064</v>
+      </c>
+      <c r="B58" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58" t="s">
+        <v>217</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>50</v>
+      </c>
+      <c r="G58">
+        <v>10001</v>
+      </c>
+      <c r="H58" t="s">
+        <v>218</v>
+      </c>
+      <c r="I58" t="s">
+        <v>34</v>
+      </c>
+      <c r="J58" t="s">
+        <v>35</v>
+      </c>
+      <c r="L58" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:12">
+      <c r="A59">
+        <v>20065</v>
+      </c>
+      <c r="B59" t="s">
+        <v>220</v>
+      </c>
+      <c r="C59" t="s">
+        <v>221</v>
+      </c>
+      <c r="D59" t="s">
+        <v>222</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>50</v>
+      </c>
+      <c r="G59">
+        <v>10001</v>
+      </c>
+      <c r="H59" t="s">
+        <v>223</v>
+      </c>
+      <c r="I59" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" t="s">
+        <v>35</v>
+      </c>
+      <c r="L59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:12">
+      <c r="A60">
+        <v>20066</v>
+      </c>
+      <c r="B60" t="s">
+        <v>224</v>
+      </c>
+      <c r="C60" t="s">
+        <v>225</v>
+      </c>
+      <c r="D60" t="s">
+        <v>226</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60">
+        <v>50</v>
+      </c>
+      <c r="G60">
+        <v>10001</v>
+      </c>
+      <c r="H60" t="s">
+        <v>227</v>
+      </c>
+      <c r="I60" t="s">
+        <v>34</v>
+      </c>
+      <c r="J60" t="s">
+        <v>35</v>
+      </c>
+      <c r="L60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:12">
+      <c r="A61">
+        <v>20067</v>
+      </c>
+      <c r="B61" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" t="s">
+        <v>229</v>
+      </c>
+      <c r="D61" t="s">
+        <v>126</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>50</v>
+      </c>
+      <c r="G61">
+        <v>10001</v>
+      </c>
+      <c r="H61" t="s">
+        <v>230</v>
+      </c>
+      <c r="I61" t="s">
+        <v>41</v>
+      </c>
+      <c r="J61" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
+      <c r="A62">
+        <v>20068</v>
+      </c>
+      <c r="B62" t="s">
+        <v>231</v>
+      </c>
+      <c r="C62" t="s">
+        <v>232</v>
+      </c>
+      <c r="D62" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>50</v>
+      </c>
+      <c r="G62">
+        <v>10001</v>
+      </c>
+      <c r="H62" t="s">
+        <v>233</v>
+      </c>
+      <c r="I62" t="s">
+        <v>41</v>
+      </c>
+      <c r="J62" t="s">
+        <v>42</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:12">
+      <c r="A63">
+        <v>20069</v>
+      </c>
+      <c r="B63" t="s">
+        <v>234</v>
+      </c>
+      <c r="C63" t="s">
+        <v>235</v>
+      </c>
+      <c r="D63" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63">
+        <v>50</v>
+      </c>
+      <c r="G63">
+        <v>10001</v>
+      </c>
+      <c r="H63" t="s">
+        <v>236</v>
+      </c>
+      <c r="I63" t="s">
+        <v>34</v>
+      </c>
+      <c r="J63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:12">
+      <c r="A64">
+        <v>20070</v>
+      </c>
+      <c r="B64" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" t="s">
+        <v>238</v>
+      </c>
+      <c r="D64" t="s">
+        <v>139</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>50</v>
+      </c>
+      <c r="G64">
+        <v>10001</v>
+      </c>
+      <c r="H64" t="s">
+        <v>239</v>
+      </c>
+      <c r="I64" t="s">
+        <v>41</v>
+      </c>
+      <c r="J64" t="s">
+        <v>42</v>
+      </c>
+      <c r="L64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:12">
+      <c r="A65">
+        <v>20071</v>
+      </c>
+      <c r="B65" t="s">
+        <v>240</v>
+      </c>
+      <c r="C65" t="s">
+        <v>241</v>
+      </c>
+      <c r="D65" t="s">
+        <v>122</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>50</v>
+      </c>
+      <c r="G65">
+        <v>10001</v>
+      </c>
+      <c r="H65" t="s">
+        <v>242</v>
+      </c>
+      <c r="I65" t="s">
+        <v>41</v>
+      </c>
+      <c r="J65" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:12">
+      <c r="A66">
+        <v>20072</v>
+      </c>
+      <c r="B66" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" t="s">
+        <v>244</v>
+      </c>
+      <c r="D66" t="s">
+        <v>245</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66">
+        <v>50</v>
+      </c>
+      <c r="G66">
+        <v>10001</v>
+      </c>
+      <c r="H66" t="s">
+        <v>246</v>
+      </c>
+      <c r="I66" t="s">
+        <v>41</v>
+      </c>
+      <c r="J66" t="s">
+        <v>42</v>
+      </c>
+      <c r="L66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:12">
+      <c r="A67">
+        <v>20073</v>
+      </c>
+      <c r="B67" t="s">
+        <v>247</v>
+      </c>
+      <c r="C67" t="s">
+        <v>248</v>
+      </c>
+      <c r="D67" t="s">
+        <v>226</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67">
+        <v>50</v>
+      </c>
+      <c r="G67">
+        <v>10001</v>
+      </c>
+      <c r="H67" t="s">
+        <v>249</v>
+      </c>
+      <c r="I67" t="s">
+        <v>41</v>
+      </c>
+      <c r="J67" t="s">
+        <v>42</v>
+      </c>
+      <c r="L67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:12">
+      <c r="A68">
+        <v>20074</v>
+      </c>
+      <c r="B68" t="s">
+        <v>250</v>
+      </c>
+      <c r="C68" t="s">
+        <v>251</v>
+      </c>
+      <c r="D68" t="s">
+        <v>139</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68">
+        <v>50</v>
+      </c>
+      <c r="G68">
+        <v>10001</v>
+      </c>
+      <c r="H68" t="s">
+        <v>252</v>
+      </c>
+      <c r="I68" t="s">
+        <v>41</v>
+      </c>
+      <c r="J68" t="s">
+        <v>42</v>
+      </c>
+      <c r="L68" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:12">
+      <c r="A69">
+        <v>20075</v>
+      </c>
+      <c r="B69" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" t="s">
+        <v>254</v>
+      </c>
+      <c r="D69" t="s">
+        <v>139</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69">
+        <v>50</v>
+      </c>
+      <c r="G69">
+        <v>10001</v>
+      </c>
+      <c r="H69" t="s">
+        <v>255</v>
+      </c>
+      <c r="I69" t="s">
+        <v>41</v>
+      </c>
+      <c r="J69" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:12">
+      <c r="A70">
+        <v>20076</v>
+      </c>
+      <c r="B70" t="s">
+        <v>256</v>
+      </c>
+      <c r="C70" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" t="s">
+        <v>126</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70">
+        <v>50</v>
+      </c>
+      <c r="G70">
+        <v>10001</v>
+      </c>
+      <c r="H70" t="s">
+        <v>258</v>
+      </c>
+      <c r="I70" t="s">
+        <v>41</v>
+      </c>
+      <c r="J70" t="s">
+        <v>42</v>
+      </c>
+      <c r="L70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:12">
+      <c r="A71">
+        <v>20077</v>
+      </c>
+      <c r="B71" t="s">
+        <v>259</v>
+      </c>
+      <c r="C71" t="s">
+        <v>260</v>
+      </c>
+      <c r="D71" t="s">
+        <v>122</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71">
+        <v>50</v>
+      </c>
+      <c r="G71">
+        <v>10001</v>
+      </c>
+      <c r="H71" t="s">
+        <v>261</v>
+      </c>
+      <c r="I71" t="s">
+        <v>41</v>
+      </c>
+      <c r="J71" t="s">
+        <v>42</v>
+      </c>
+      <c r="L71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:12">
+      <c r="A72">
+        <v>20078</v>
+      </c>
+      <c r="B72" t="s">
+        <v>262</v>
+      </c>
+      <c r="C72" t="s">
+        <v>263</v>
+      </c>
+      <c r="D72" t="s">
+        <v>122</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72">
+        <v>50</v>
+      </c>
+      <c r="G72">
+        <v>10001</v>
+      </c>
+      <c r="H72" t="s">
+        <v>264</v>
+      </c>
+      <c r="I72" t="s">
+        <v>34</v>
+      </c>
+      <c r="J72" t="s">
+        <v>42</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:12">
+      <c r="A73">
+        <v>20079</v>
+      </c>
+      <c r="B73" t="s">
+        <v>265</v>
+      </c>
+      <c r="C73" t="s">
+        <v>266</v>
+      </c>
+      <c r="D73" t="s">
+        <v>122</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73">
+        <v>50</v>
+      </c>
+      <c r="G73">
+        <v>10001</v>
+      </c>
+      <c r="H73" t="s">
+        <v>267</v>
+      </c>
+      <c r="I73" t="s">
+        <v>41</v>
+      </c>
+      <c r="J73" t="s">
+        <v>63</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:12">
+      <c r="A74">
+        <v>20080</v>
+      </c>
+      <c r="B74" t="s">
+        <v>268</v>
+      </c>
+      <c r="C74" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" t="s">
+        <v>119</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74">
+        <v>50</v>
+      </c>
+      <c r="G74">
+        <v>10001</v>
+      </c>
+      <c r="H74" t="s">
+        <v>270</v>
+      </c>
+      <c r="I74" t="s">
+        <v>41</v>
+      </c>
+      <c r="J74" t="s">
+        <v>63</v>
+      </c>
+      <c r="L74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:12">
+      <c r="A75">
+        <v>20081</v>
+      </c>
+      <c r="B75" t="s">
+        <v>271</v>
+      </c>
+      <c r="C75" t="s">
+        <v>272</v>
+      </c>
+      <c r="D75" t="s">
+        <v>119</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75">
+        <v>50</v>
+      </c>
+      <c r="G75">
+        <v>10001</v>
+      </c>
+      <c r="H75" t="s">
+        <v>273</v>
+      </c>
+      <c r="I75" t="s">
+        <v>41</v>
+      </c>
+      <c r="J75" t="s">
+        <v>63</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:12">
+      <c r="A76">
+        <v>20082</v>
+      </c>
+      <c r="B76" t="s">
+        <v>274</v>
+      </c>
+      <c r="C76" t="s">
+        <v>275</v>
+      </c>
+      <c r="D76" t="s">
+        <v>139</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76">
+        <v>50</v>
+      </c>
+      <c r="G76">
+        <v>10001</v>
+      </c>
+      <c r="H76" t="s">
+        <v>276</v>
+      </c>
+      <c r="I76" t="s">
+        <v>41</v>
+      </c>
+      <c r="J76" t="s">
+        <v>63</v>
+      </c>
+      <c r="L76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:12">
+      <c r="A77">
+        <v>20083</v>
+      </c>
+      <c r="B77" t="s">
+        <v>277</v>
+      </c>
+      <c r="C77" t="s">
+        <v>278</v>
+      </c>
+      <c r="D77" t="s">
+        <v>119</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77">
+        <v>50</v>
+      </c>
+      <c r="G77">
+        <v>10001</v>
+      </c>
+      <c r="H77" t="s">
+        <v>279</v>
+      </c>
+      <c r="I77" t="s">
+        <v>41</v>
+      </c>
+      <c r="J77" t="s">
+        <v>63</v>
+      </c>
+      <c r="L77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:12">
+      <c r="A78">
+        <v>20084</v>
+      </c>
+      <c r="B78" t="s">
+        <v>280</v>
+      </c>
+      <c r="C78" t="s">
+        <v>281</v>
+      </c>
+      <c r="D78" t="s">
+        <v>222</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>50</v>
+      </c>
+      <c r="G78">
+        <v>10001</v>
+      </c>
+      <c r="H78" t="s">
+        <v>282</v>
+      </c>
+      <c r="I78" t="s">
+        <v>41</v>
+      </c>
+      <c r="J78" t="s">
+        <v>63</v>
+      </c>
+      <c r="L78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:12">
+      <c r="A79">
+        <v>20085</v>
+      </c>
+      <c r="B79" t="s">
+        <v>283</v>
+      </c>
+      <c r="C79" t="s">
+        <v>284</v>
+      </c>
+      <c r="D79" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="F79">
+        <v>50</v>
+      </c>
+      <c r="G79">
+        <v>10001</v>
+      </c>
+      <c r="H79" t="s">
+        <v>285</v>
+      </c>
+      <c r="I79" t="s">
+        <v>41</v>
+      </c>
+      <c r="J79" t="s">
+        <v>63</v>
+      </c>
+      <c r="L79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:12">
+      <c r="A80">
+        <v>20086</v>
+      </c>
+      <c r="B80" t="s">
+        <v>286</v>
+      </c>
+      <c r="C80" t="s">
+        <v>287</v>
+      </c>
+      <c r="D80" t="s">
+        <v>139</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="F80">
+        <v>50</v>
+      </c>
+      <c r="G80">
+        <v>10001</v>
+      </c>
+      <c r="H80" t="s">
+        <v>288</v>
+      </c>
+      <c r="I80" t="s">
+        <v>41</v>
+      </c>
+      <c r="J80" t="s">
+        <v>63</v>
+      </c>
+      <c r="L80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:12">
+      <c r="A81">
+        <v>20087</v>
+      </c>
+      <c r="B81" t="s">
+        <v>289</v>
+      </c>
+      <c r="C81" t="s">
+        <v>290</v>
+      </c>
+      <c r="D81" t="s">
+        <v>139</v>
+      </c>
+      <c r="E81">
+        <v>3</v>
+      </c>
+      <c r="F81">
+        <v>50</v>
+      </c>
+      <c r="G81">
+        <v>10001</v>
+      </c>
+      <c r="H81" t="s">
+        <v>291</v>
+      </c>
+      <c r="I81" t="s">
+        <v>34</v>
+      </c>
+      <c r="J81" t="s">
+        <v>35</v>
+      </c>
+      <c r="L81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:12">
+      <c r="A82">
+        <v>20088</v>
+      </c>
+      <c r="B82" t="s">
+        <v>292</v>
+      </c>
+      <c r="C82" t="s">
+        <v>293</v>
+      </c>
+      <c r="D82" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+      <c r="F82">
+        <v>50</v>
+      </c>
+      <c r="G82">
+        <v>10001</v>
+      </c>
+      <c r="H82" t="s">
+        <v>294</v>
+      </c>
+      <c r="I82" t="s">
+        <v>34</v>
+      </c>
+      <c r="J82" t="s">
+        <v>35</v>
+      </c>
+      <c r="L82" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:12">
+      <c r="A83">
+        <v>20089</v>
+      </c>
+      <c r="B83" t="s">
+        <v>295</v>
+      </c>
+      <c r="C83" t="s">
+        <v>296</v>
+      </c>
+      <c r="D83" t="s">
+        <v>115</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
+      </c>
+      <c r="F83">
+        <v>50</v>
+      </c>
+      <c r="G83">
+        <v>10001</v>
+      </c>
+      <c r="H83" t="s">
+        <v>297</v>
+      </c>
+      <c r="I83" t="s">
+        <v>34</v>
+      </c>
+      <c r="J83" t="s">
+        <v>35</v>
+      </c>
+      <c r="L83" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:12">
+      <c r="A84">
+        <v>20090</v>
+      </c>
+      <c r="B84" t="s">
+        <v>298</v>
+      </c>
+      <c r="C84" t="s">
+        <v>299</v>
+      </c>
+      <c r="D84" t="s">
+        <v>300</v>
+      </c>
+      <c r="E84">
+        <v>3</v>
+      </c>
+      <c r="F84">
+        <v>50</v>
+      </c>
+      <c r="G84">
+        <v>10001</v>
+      </c>
+      <c r="H84" t="s">
+        <v>301</v>
+      </c>
+      <c r="I84" t="s">
+        <v>34</v>
+      </c>
+      <c r="J84" t="s">
+        <v>35</v>
+      </c>
+      <c r="L84" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:12">
+      <c r="A85">
+        <v>20091</v>
+      </c>
+      <c r="B85" t="s">
+        <v>302</v>
+      </c>
+      <c r="C85" t="s">
+        <v>303</v>
+      </c>
+      <c r="D85" t="s">
+        <v>126</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+      <c r="F85">
+        <v>50</v>
+      </c>
+      <c r="G85">
+        <v>10001</v>
+      </c>
+      <c r="H85" t="s">
+        <v>304</v>
+      </c>
+      <c r="I85" t="s">
+        <v>34</v>
+      </c>
+      <c r="J85" t="s">
+        <v>35</v>
+      </c>
+      <c r="L85" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:12">
+      <c r="A86">
+        <v>20092</v>
+      </c>
+      <c r="B86" t="s">
+        <v>305</v>
+      </c>
+      <c r="C86" t="s">
+        <v>306</v>
+      </c>
+      <c r="D86" t="s">
+        <v>115</v>
+      </c>
+      <c r="E86">
+        <v>3</v>
+      </c>
+      <c r="F86">
+        <v>50</v>
+      </c>
+      <c r="G86">
+        <v>10001</v>
+      </c>
+      <c r="H86" t="s">
+        <v>307</v>
+      </c>
+      <c r="I86" t="s">
+        <v>34</v>
+      </c>
+      <c r="J86" t="s">
+        <v>35</v>
+      </c>
+      <c r="L86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:12">
+      <c r="A87">
+        <v>20093</v>
+      </c>
+      <c r="B87" t="s">
+        <v>308</v>
+      </c>
+      <c r="C87" t="s">
+        <v>309</v>
+      </c>
+      <c r="D87" t="s">
+        <v>119</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+      <c r="F87">
+        <v>50</v>
+      </c>
+      <c r="G87">
+        <v>10001</v>
+      </c>
+      <c r="H87" t="s">
+        <v>310</v>
+      </c>
+      <c r="I87" t="s">
+        <v>34</v>
+      </c>
+      <c r="J87" t="s">
+        <v>35</v>
+      </c>
+      <c r="L87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:12">
+      <c r="A88">
+        <v>20094</v>
+      </c>
+      <c r="B88" t="s">
+        <v>311</v>
+      </c>
+      <c r="C88" t="s">
+        <v>312</v>
+      </c>
+      <c r="D88" t="s">
+        <v>126</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88">
+        <v>50</v>
+      </c>
+      <c r="G88">
+        <v>10001</v>
+      </c>
+      <c r="H88" t="s">
+        <v>313</v>
+      </c>
+      <c r="I88" t="s">
+        <v>41</v>
+      </c>
+      <c r="J88" t="s">
+        <v>42</v>
+      </c>
+      <c r="L88" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:12">
+      <c r="A89">
+        <v>20095</v>
+      </c>
+      <c r="B89" t="s">
+        <v>314</v>
+      </c>
+      <c r="C89" t="s">
+        <v>315</v>
+      </c>
+      <c r="D89" t="s">
+        <v>316</v>
+      </c>
+      <c r="E89">
+        <v>3</v>
+      </c>
+      <c r="F89">
+        <v>50</v>
+      </c>
+      <c r="G89">
+        <v>10001</v>
+      </c>
+      <c r="H89" t="s">
+        <v>317</v>
+      </c>
+      <c r="I89" t="s">
+        <v>41</v>
+      </c>
+      <c r="J89" t="s">
+        <v>42</v>
+      </c>
+      <c r="L89" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:12">
+      <c r="A90">
+        <v>20096</v>
+      </c>
+      <c r="B90" t="s">
+        <v>318</v>
+      </c>
+      <c r="C90" t="s">
+        <v>319</v>
+      </c>
+      <c r="D90" t="s">
+        <v>316</v>
+      </c>
+      <c r="E90">
+        <v>3</v>
+      </c>
+      <c r="F90">
+        <v>50</v>
+      </c>
+      <c r="G90">
+        <v>10001</v>
+      </c>
+      <c r="H90" t="s">
+        <v>320</v>
+      </c>
+      <c r="I90" t="s">
+        <v>41</v>
+      </c>
+      <c r="J90" t="s">
+        <v>42</v>
+      </c>
+      <c r="L90" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:12">
+      <c r="A91">
+        <v>20097</v>
+      </c>
+      <c r="B91" t="s">
+        <v>321</v>
+      </c>
+      <c r="C91" t="s">
+        <v>322</v>
+      </c>
+      <c r="D91" t="s">
+        <v>126</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="F91">
+        <v>50</v>
+      </c>
+      <c r="G91">
+        <v>10001</v>
+      </c>
+      <c r="H91" t="s">
+        <v>323</v>
+      </c>
+      <c r="I91" t="s">
+        <v>41</v>
+      </c>
+      <c r="J91" t="s">
+        <v>42</v>
+      </c>
+      <c r="L91" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:12">
+      <c r="A92">
+        <v>20098</v>
+      </c>
+      <c r="B92" t="s">
+        <v>324</v>
+      </c>
+      <c r="C92" t="s">
+        <v>325</v>
+      </c>
+      <c r="D92" t="s">
+        <v>139</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>50</v>
+      </c>
+      <c r="G92">
+        <v>10001</v>
+      </c>
+      <c r="H92" t="s">
+        <v>326</v>
+      </c>
+      <c r="I92" t="s">
+        <v>41</v>
+      </c>
+      <c r="J92" t="s">
+        <v>42</v>
+      </c>
+      <c r="L92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:12">
+      <c r="A93">
+        <v>20099</v>
+      </c>
+      <c r="B93" t="s">
+        <v>327</v>
+      </c>
+      <c r="C93" t="s">
+        <v>328</v>
+      </c>
+      <c r="D93" t="s">
+        <v>126</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <v>50</v>
+      </c>
+      <c r="G93">
+        <v>10001</v>
+      </c>
+      <c r="H93" t="s">
+        <v>329</v>
+      </c>
+      <c r="I93" t="s">
+        <v>41</v>
+      </c>
+      <c r="J93" t="s">
+        <v>42</v>
+      </c>
+      <c r="L93" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:12">
+      <c r="A94">
+        <v>20100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>330</v>
+      </c>
+      <c r="C94" t="s">
+        <v>331</v>
+      </c>
+      <c r="D94" t="s">
+        <v>139</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+      <c r="F94">
+        <v>50</v>
+      </c>
+      <c r="G94">
+        <v>10001</v>
+      </c>
+      <c r="H94" t="s">
+        <v>332</v>
+      </c>
+      <c r="I94" t="s">
+        <v>41</v>
+      </c>
+      <c r="J94" t="s">
+        <v>42</v>
+      </c>
+      <c r="L94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:12">
+      <c r="A95">
+        <v>20101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>333</v>
+      </c>
+      <c r="C95" t="s">
+        <v>334</v>
+      </c>
+      <c r="D95" t="s">
+        <v>335</v>
+      </c>
+      <c r="E95">
+        <v>3</v>
+      </c>
+      <c r="F95">
+        <v>50</v>
+      </c>
+      <c r="G95">
+        <v>10001</v>
+      </c>
+      <c r="H95" t="s">
+        <v>336</v>
+      </c>
+      <c r="I95" t="s">
+        <v>41</v>
+      </c>
+      <c r="J95" t="s">
+        <v>63</v>
+      </c>
+      <c r="L95" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:12">
+      <c r="A96">
+        <v>20102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>337</v>
+      </c>
+      <c r="C96" t="s">
+        <v>338</v>
+      </c>
+      <c r="D96" t="s">
+        <v>119</v>
+      </c>
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96">
+        <v>50</v>
+      </c>
+      <c r="G96">
+        <v>10001</v>
+      </c>
+      <c r="H96" t="s">
+        <v>339</v>
+      </c>
+      <c r="I96" t="s">
+        <v>41</v>
+      </c>
+      <c r="J96" t="s">
+        <v>63</v>
+      </c>
+      <c r="L96" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:12">
+      <c r="A97">
+        <v>20103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>340</v>
+      </c>
+      <c r="C97" t="s">
+        <v>341</v>
+      </c>
+      <c r="D97" t="s">
+        <v>119</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="F97">
+        <v>50</v>
+      </c>
+      <c r="G97">
+        <v>10001</v>
+      </c>
+      <c r="H97" t="s">
+        <v>342</v>
+      </c>
+      <c r="I97" t="s">
+        <v>41</v>
+      </c>
+      <c r="J97" t="s">
+        <v>63</v>
+      </c>
+      <c r="L97" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:12">
+      <c r="A98">
+        <v>20104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>343</v>
+      </c>
+      <c r="C98" t="s">
+        <v>344</v>
+      </c>
+      <c r="D98" t="s">
+        <v>245</v>
+      </c>
+      <c r="E98">
+        <v>3</v>
+      </c>
+      <c r="F98">
+        <v>50</v>
+      </c>
+      <c r="G98">
+        <v>10001</v>
+      </c>
+      <c r="H98" t="s">
+        <v>345</v>
+      </c>
+      <c r="I98" t="s">
+        <v>41</v>
+      </c>
+      <c r="J98" t="s">
+        <v>63</v>
+      </c>
+      <c r="L98" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:12">
+      <c r="A99">
+        <v>20105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>346</v>
+      </c>
+      <c r="C99" t="s">
+        <v>347</v>
+      </c>
+      <c r="D99" t="s">
+        <v>189</v>
+      </c>
+      <c r="E99">
+        <v>3</v>
+      </c>
+      <c r="F99">
+        <v>50</v>
+      </c>
+      <c r="G99">
+        <v>10001</v>
+      </c>
+      <c r="H99" t="s">
+        <v>348</v>
+      </c>
+      <c r="I99" t="s">
+        <v>41</v>
+      </c>
+      <c r="J99" t="s">
+        <v>63</v>
+      </c>
+      <c r="L99" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:12">
+      <c r="A100">
+        <v>20106</v>
+      </c>
+      <c r="B100" t="s">
+        <v>349</v>
+      </c>
+      <c r="C100" t="s">
+        <v>350</v>
+      </c>
+      <c r="D100" t="s">
+        <v>245</v>
+      </c>
+      <c r="E100">
+        <v>3</v>
+      </c>
+      <c r="F100">
+        <v>50</v>
+      </c>
+      <c r="G100">
+        <v>10001</v>
+      </c>
+      <c r="H100" t="s">
+        <v>351</v>
+      </c>
+      <c r="I100" t="s">
+        <v>41</v>
+      </c>
+      <c r="J100" t="s">
+        <v>63</v>
+      </c>
+      <c r="L100" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:12">
+      <c r="A101">
+        <v>20107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>352</v>
+      </c>
+      <c r="C101" t="s">
+        <v>353</v>
+      </c>
+      <c r="D101" t="s">
+        <v>226</v>
+      </c>
+      <c r="E101">
+        <v>3</v>
+      </c>
+      <c r="F101">
+        <v>50</v>
+      </c>
+      <c r="G101">
+        <v>10001</v>
+      </c>
+      <c r="H101" t="s">
+        <v>354</v>
+      </c>
+      <c r="I101" t="s">
+        <v>41</v>
+      </c>
+      <c r="J101" t="s">
+        <v>63</v>
+      </c>
+      <c r="L101" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:12">
+      <c r="A102">
+        <v>20108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>355</v>
+      </c>
+      <c r="C102" t="s">
+        <v>356</v>
+      </c>
+      <c r="D102" t="s">
+        <v>245</v>
+      </c>
+      <c r="E102">
+        <v>3</v>
+      </c>
+      <c r="F102">
+        <v>50</v>
+      </c>
+      <c r="G102">
+        <v>10001</v>
+      </c>
+      <c r="H102" t="s">
+        <v>357</v>
+      </c>
+      <c r="I102" t="s">
+        <v>41</v>
+      </c>
+      <c r="J102" t="s">
+        <v>63</v>
+      </c>
+      <c r="L102" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:12">
+      <c r="A103">
+        <v>20109</v>
+      </c>
+      <c r="B103" t="s">
+        <v>358</v>
+      </c>
+      <c r="C103" t="s">
+        <v>359</v>
+      </c>
+      <c r="D103" t="s">
+        <v>316</v>
+      </c>
+      <c r="E103">
+        <v>3</v>
+      </c>
+      <c r="F103">
+        <v>50</v>
+      </c>
+      <c r="G103">
+        <v>10001</v>
+      </c>
+      <c r="H103" t="s">
+        <v>360</v>
+      </c>
+      <c r="I103" t="s">
+        <v>41</v>
+      </c>
+      <c r="J103" t="s">
+        <v>63</v>
+      </c>
+      <c r="L103" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:12">
+      <c r="A104">
+        <v>20110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>361</v>
+      </c>
+      <c r="C104" t="s">
+        <v>362</v>
+      </c>
+      <c r="D104" t="s">
+        <v>119</v>
+      </c>
+      <c r="E104">
+        <v>3</v>
+      </c>
+      <c r="F104">
+        <v>50</v>
+      </c>
+      <c r="G104">
+        <v>10001</v>
+      </c>
+      <c r="H104" t="s">
+        <v>363</v>
+      </c>
+      <c r="I104" t="s">
+        <v>34</v>
+      </c>
+      <c r="J104" t="s">
+        <v>35</v>
+      </c>
+      <c r="L104" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:12">
+      <c r="A105">
+        <v>20111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>365</v>
+      </c>
+      <c r="C105" t="s">
+        <v>366</v>
+      </c>
+      <c r="D105" t="s">
+        <v>367</v>
+      </c>
+      <c r="E105">
+        <v>3</v>
+      </c>
+      <c r="F105">
+        <v>50</v>
+      </c>
+      <c r="G105">
+        <v>10001</v>
+      </c>
+      <c r="H105" t="s">
+        <v>368</v>
+      </c>
+      <c r="I105" t="s">
+        <v>41</v>
+      </c>
+      <c r="J105" t="s">
+        <v>63</v>
+      </c>
+      <c r="L105" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:12">
+      <c r="A106">
+        <v>20112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>369</v>
+      </c>
+      <c r="C106" t="s">
+        <v>370</v>
+      </c>
+      <c r="D106" t="s">
+        <v>119</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106">
+        <v>50</v>
+      </c>
+      <c r="G106">
+        <v>10001</v>
+      </c>
+      <c r="H106" t="s">
+        <v>371</v>
+      </c>
+      <c r="I106" t="s">
+        <v>34</v>
+      </c>
+      <c r="J106" t="s">
+        <v>35</v>
+      </c>
+      <c r="L106" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/策划/excel/2_Card.xlsx
+++ b/策划/excel/2_Card.xlsx
@@ -1,33 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\策划\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView windowWidth="30435" windowHeight="15735"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30435" windowHeight="15735"/>
   </bookViews>
   <sheets>
-    <sheet name="2_Card" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="2_Card" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -220,7 +202,7 @@
     <t>[30007,30005,30008]</t>
   </si>
   <si>
-    <t>[{"id":"e_rebalance_8","type":210015,"target":"SELF","params":{"stat":200001,"amount":1,"duration":"COMBAT"},"children":[],"elseEffects":[]},{"id":"e_card_57","type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_55","type":210001,"target":"ENEMY","params":{"amount":3,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]},{"id":"e_card_56","type":210002,"target":"SELF","params":{"amount":2,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+    <t>[{"id":"abilityBuff20017","type":210010,"target":"SELF","params":{"status":200021,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>POWER</t>
@@ -322,7 +304,7 @@
     <t>[30010,30011,30010]</t>
   </si>
   <si>
-    <t>[{"id":"e_card_87","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_91","type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_rebalance_15","type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[]},{"id":"e_card_89","type":210003,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]},{"id":"e_card_90","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+    <t>[{"id":"abilityBuff20026","type":210010,"target":"SELF","params":{"status":200022,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>投羽连击</t>
@@ -370,13 +352,13 @@
     <t>[30009,30010,30011,30012]</t>
   </si>
   <si>
-    <t>[{"id":"e_card_112","type":210010,"target":"ENEMY","params":{"status":200006,"stacks":5,"duration":"DEFAULT"},"children":[],"elseEffects":[]},{"id":"e_card_114","type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"id":"e_card_113","type":210001,"target":"ENEMY","params":{"amount":4,"hits":1,"damageKind":"ATTACK","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]},{"id":"e_card_117","type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"id":"e_card_115","type":210003,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]},{"id":"e_rebalance_19","type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+    <t>[{"id":"abilityBuff20030","type":210010,"target":"SELF","params":{"status":200023,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>痛击</t>
   </si>
   <si>
-    <t>造成8点伤害。
+    <t xml:space="preserve">造成8点伤害。
 给予2层易伤。</t>
   </si>
   <si>
@@ -410,7 +392,7 @@
     <t>愤怒</t>
   </si>
   <si>
-    <t>造成6点伤害。
+    <t xml:space="preserve">造成6点伤害。
 将一张此牌的复制品加入你的弃牌堆。</t>
   </si>
   <si>
@@ -432,7 +414,7 @@
     <t>突破</t>
   </si>
   <si>
-    <t>失去1点生命。
+    <t xml:space="preserve">失去1点生命。
 对敌人造成9点伤害。</t>
   </si>
   <si>
@@ -442,7 +424,7 @@
     <t>余烬</t>
   </si>
   <si>
-    <t>造成18点伤害。
+    <t xml:space="preserve">造成18点伤害。
 随机消耗1张牌。</t>
   </si>
   <si>
@@ -452,7 +434,7 @@
     <t>头槌</t>
   </si>
   <si>
-    <t>造成6点伤害。
+    <t xml:space="preserve">造成6点伤害。
 将弃牌堆中的1张牌放到抽牌堆顶部。</t>
   </si>
   <si>
@@ -465,7 +447,7 @@
     <t>铁斩波</t>
   </si>
   <si>
-    <t>获得6点格挡。
+    <t xml:space="preserve">获得6点格挡。
 造成3点伤害。</t>
   </si>
   <si>
@@ -475,7 +457,7 @@
     <t>熔融之拳</t>
   </si>
   <si>
-    <t>造成10点伤害。
+    <t xml:space="preserve">造成10点伤害。
 将该敌人身上的易伤层数翻倍。
 消耗。</t>
   </si>
@@ -489,7 +471,7 @@
     <t>完美打击</t>
   </si>
   <si>
-    <t>造成6点伤害。
+    <t xml:space="preserve">造成6点伤害。
 你每有一张名字中含有“打击”的牌，伤害+2。</t>
   </si>
   <si>
@@ -499,7 +481,7 @@
     <t>剑柄打击</t>
   </si>
   <si>
-    <t>造成6点伤害。
+    <t xml:space="preserve">造成6点伤害。
 抽1张牌。</t>
   </si>
   <si>
@@ -509,7 +491,7 @@
     <t>预备打击</t>
   </si>
   <si>
-    <t>造成7点伤害。
+    <t xml:space="preserve">造成7点伤害。
 在本回合内获得2点力量。</t>
   </si>
   <si>
@@ -528,7 +510,7 @@
     <t>闪电霹雳</t>
   </si>
   <si>
-    <t>造成3点伤害。
+    <t xml:space="preserve">造成3点伤害。
 给予敌人1层虚弱。</t>
   </si>
   <si>
@@ -547,7 +529,7 @@
     <t>血墙</t>
   </si>
   <si>
-    <t>失去2点生命。
+    <t xml:space="preserve">失去2点生命。
 获得16点格挡。</t>
   </si>
   <si>
@@ -557,7 +539,7 @@
     <t>放血</t>
   </si>
   <si>
-    <t>失去3点生命。
+    <t xml:space="preserve">失去3点生命。
 获得2点能量。</t>
   </si>
   <si>
@@ -576,7 +558,7 @@
     <t>耸肩无视</t>
   </si>
   <si>
-    <t>获得8点格挡。
+    <t xml:space="preserve">获得8点格挡。
 抽1张牌。</t>
   </si>
   <si>
@@ -586,7 +568,7 @@
     <t>战栗</t>
   </si>
   <si>
-    <t>给予3层易伤。
+    <t xml:space="preserve">给予3层易伤。
 消耗。</t>
   </si>
   <si>
@@ -596,7 +578,7 @@
     <t>坚毅</t>
   </si>
   <si>
-    <t>获得7点格挡。
+    <t xml:space="preserve">获得7点格挡。
 随机消耗1张牌。</t>
   </si>
   <si>
@@ -606,7 +588,7 @@
     <t>灰烬打击</t>
   </si>
   <si>
-    <t>造成6点伤害。
+    <t xml:space="preserve">造成6点伤害。
 你的消耗牌堆中每有一张牌，伤害增加3。</t>
   </si>
   <si>
@@ -628,7 +610,7 @@
     <t>欺凌</t>
   </si>
   <si>
-    <t>造成4点伤害。
+    <t xml:space="preserve">造成4点伤害。
 该敌人身上每有一层易伤就额外造成2点伤害。</t>
   </si>
   <si>
@@ -638,7 +620,7 @@
     <t>拆卸</t>
   </si>
   <si>
-    <t>造成5点伤害。
+    <t xml:space="preserve">造成5点伤害。
 如果敌人有易伤状态，则改为造成2次伤害。</t>
   </si>
   <si>
@@ -648,7 +630,7 @@
     <t>与我一战！</t>
   </si>
   <si>
-    <t>造成5点伤害两次。
+    <t xml:space="preserve">造成5点伤害两次。
 获得3点力量。
 该敌人获得1点力量。</t>
   </si>
@@ -659,7 +641,7 @@
     <t>御血术</t>
   </si>
   <si>
-    <t>失去2点生命。
+    <t xml:space="preserve">失去2点生命。
 造成15点伤害。</t>
   </si>
   <si>
@@ -669,7 +651,7 @@
     <t>彼岸咆哮</t>
   </si>
   <si>
-    <t>造成16点伤害。
+    <t xml:space="preserve">造成16点伤害。
 回合结束时，若此牌位于消耗牌堆，则无需骰子对当前敌人结算此牌的伤害。</t>
   </si>
   <si>
@@ -679,7 +661,7 @@
     <t>劫掠</t>
   </si>
   <si>
-    <t>造成5点伤害。
+    <t xml:space="preserve">造成5点伤害。
 连续抽牌，直到抽到1张非攻击牌或手牌达到10张；无牌可抽时停止。</t>
   </si>
   <si>
@@ -689,7 +671,7 @@
     <t>暴走</t>
   </si>
   <si>
-    <t>造成9点伤害。
+    <t xml:space="preserve">造成9点伤害。
 将这张牌在本场战斗中的伤害增加5。</t>
   </si>
   <si>
@@ -699,7 +681,7 @@
     <t>怨恨</t>
   </si>
   <si>
-    <t>造成5点伤害。
+    <t xml:space="preserve">造成5点伤害。
 如果你在本回合失去过生命值，
 则攻击2次。</t>
   </si>
@@ -710,7 +692,7 @@
     <t>踩踏</t>
   </si>
   <si>
-    <t>造成12点伤害。
+    <t xml:space="preserve">造成12点伤害。
 本回合每打出过1张攻击牌，此牌少需要1颗斧头骰子；最多减免2颗斧头骰子，仍需要1颗符文骰子。</t>
   </si>
   <si>
@@ -726,7 +708,7 @@
     <t>无情猛攻</t>
   </si>
   <si>
-    <t>造成14点伤害。
+    <t xml:space="preserve">造成14点伤害。
 你打出的下一张攻击牌无需骰子。</t>
   </si>
   <si>
@@ -739,7 +721,7 @@
     <t>上勾拳</t>
   </si>
   <si>
-    <t>造成10点伤害。
+    <t xml:space="preserve">造成10点伤害。
 给予敌人1层虚弱。
 给予敌人1层易伤。</t>
   </si>
@@ -753,7 +735,7 @@
     <t>战斗专注</t>
   </si>
   <si>
-    <t>抽3张牌。
+    <t xml:space="preserve">抽3张牌。
 你在本回合内不能再抽任何牌。</t>
   </si>
   <si>
@@ -763,7 +745,7 @@
     <t>燃烧契约</t>
   </si>
   <si>
-    <t>消耗1张牌。
+    <t xml:space="preserve">消耗1张牌。
 抽2张牌。</t>
   </si>
   <si>
@@ -773,7 +755,7 @@
     <t>主宰</t>
   </si>
   <si>
-    <t>给予1层易伤。
+    <t xml:space="preserve">给予1层易伤。
 敌人身上每有一层易伤，就获得1点力量。
 消耗。</t>
   </si>
@@ -784,7 +766,7 @@
     <t>战鼓</t>
   </si>
   <si>
-    <t>抽2张牌。
+    <t xml:space="preserve">抽2张牌。
 这张牌被消耗时，获得2点能量。</t>
   </si>
   <si>
@@ -794,7 +776,7 @@
     <t>邪眼</t>
   </si>
   <si>
-    <t>获得8点格挡。
+    <t xml:space="preserve">获得8点格挡。
 如果你在本回合消耗过卡牌，则额外获得8点格挡。</t>
   </si>
   <si>
@@ -804,7 +786,7 @@
     <t>跃跃欲试</t>
   </si>
   <si>
-    <t>你的手牌中每有一张攻击牌，就获得1点能量。
+    <t xml:space="preserve">你的手牌中每有一张攻击牌，就获得1点能量。
 你在本回合内
 不能再获得能量。</t>
   </si>
@@ -818,7 +800,7 @@
     <t>火焰屏障</t>
   </si>
   <si>
-    <t>获得12点格挡。
+    <t xml:space="preserve">获得12点格挡。
 你在这个回合每受到一次攻击，都会对攻击者造成4点伤害。</t>
   </si>
   <si>
@@ -828,7 +810,7 @@
     <t>被遗忘的仪式</t>
   </si>
   <si>
-    <t>如果你在本回合消耗过卡牌，则获得3点能量。
+    <t xml:space="preserve">如果你在本回合消耗过卡牌，则获得3点能量。
 消耗。</t>
   </si>
   <si>
@@ -838,7 +820,7 @@
     <t>地狱之刃</t>
   </si>
   <si>
-    <t>将1张随机战士攻击牌加入手牌。
+    <t xml:space="preserve">将1张随机战士攻击牌加入手牌。
 这张生成的牌在本回合首次打出时无需骰子。
 消耗。</t>
   </si>
@@ -867,7 +849,7 @@
     <t>挑衅</t>
   </si>
   <si>
-    <t>获得7点格挡。
+    <t xml:space="preserve">获得7点格挡。
 给予敌人1层虚弱。</t>
   </si>
   <si>
@@ -880,17 +862,17 @@
     <t>每当有一张牌被消耗时，获得3点格挡。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_EXHAUST","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":3,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect86"}],"elseEffects":[],"id":"warriorEffect85"}]</t>
+    <t>[{"id":"abilityBuff20079","type":210010,"target":"SELF","params":{"status":200024,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>狱火</t>
   </si>
   <si>
-    <t>在你的回合开始时，失去1点生命。
+    <t xml:space="preserve">在你的回合开始时，失去1点生命。
 每当你在你的回合内失去生命时，对敌人造成6点伤害。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210004,"target":"SELF","params":{"amount":1,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect88"}],"elseEffects":[],"id":"warriorEffect87"},{"type":210022,"target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@battle.playerTurn","cmp":"==","rhs":1}]},"id":"warriorEffect90"}],"elseEffects":[],"id":"warriorEffect89"}]</t>
+    <t>[{"id":"abilityBuff20080","type":210010,"target":"SELF","params":{"status":200025,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>燃烧</t>
@@ -908,7 +890,7 @@
     <t>将你在每回合打出的第三张攻击牌的复制品加入你的手牌。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210042,"target":"SELF","params":{"source":"EVENT","pile":"HAND"},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@event.attackCount","cmp":"==","rhs":3}]},"id":"warriorEffect93"}],"elseEffects":[],"id":"warriorEffect92"}]</t>
+    <t>[{"id":"abilityBuff20082","type":210010,"target":"SELF","params":{"status":200026,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>撕裂</t>
@@ -917,7 +899,7 @@
     <t>每当你在你的回合失去生命值时, 获得1点力量。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[],"condition":{"op":"AND","rules":[{"lhs":"@battle.playerTurn","cmp":"==","rhs":1}]},"id":"warriorEffect95"}],"elseEffects":[],"id":"warriorEffect94"}]</t>
+    <t>[{"id":"abilityBuff20083","type":210010,"target":"SELF","params":{"status":200027,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>惊逃</t>
@@ -926,7 +908,7 @@
     <t>回合结束时，随机打出手牌中的1张攻击牌攻击当前敌人，不消耗骰子。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210043,"target":"SELF","params":{"pile":"HAND","mode":"RANDOM_ATTACK","exhaustAfter":false},"children":[],"elseEffects":[],"id":"warriorEffect97"}],"elseEffects":[],"id":"warriorEffect96"}]</t>
+    <t>[{"id":"abilityBuff20084","type":210010,"target":"SELF","params":{"status":200028,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>岩石铠甲</t>
@@ -944,7 +926,7 @@
     <t>每当你给予易伤时，抽1张牌。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_STATUS_APPLIED","scope":"COMBAT","limit":0,"filter":{"status":200004}},"children":[{"type":210038,"target":"SELF","params":{"count":1,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect100"}],"elseEffects":[],"id":"warriorEffect99"}]</t>
+    <t>[{"id":"abilityBuff20086","type":210010,"target":"SELF","params":{"status":200029,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>焚烧</t>
@@ -959,7 +941,7 @@
     <t>狂宴</t>
   </si>
   <si>
-    <t>造成10点伤害。
+    <t xml:space="preserve">造成10点伤害。
 斩杀时，永久获得3点最大生命值。
 消耗。</t>
   </si>
@@ -970,7 +952,7 @@
     <t>恶魔之焰</t>
   </si>
   <si>
-    <t>消耗所有手牌。
+    <t xml:space="preserve">消耗所有手牌。
 每张被消耗的牌造成7点伤害。
 消耗。</t>
   </si>
@@ -981,7 +963,7 @@
     <t>凌虐</t>
   </si>
   <si>
-    <t>造成15点伤害。
+    <t xml:space="preserve">造成15点伤害。
 敌人失去10点力量，直到敌人的本次行动结束后恢复。</t>
   </si>
   <si>
@@ -994,7 +976,7 @@
     <t>契约终结</t>
   </si>
   <si>
-    <t>如果你的消耗牌堆拥有大于等于3张牌，
+    <t xml:space="preserve">如果你的消耗牌堆拥有大于等于3张牌，
 则对敌人造成17点伤害。</t>
   </si>
   <si>
@@ -1004,7 +986,7 @@
     <t>扯碎</t>
   </si>
   <si>
-    <t>造成5点伤害。
+    <t xml:space="preserve">造成5点伤害。
 在本场战斗中，你每失去过一次生命值，这张牌就额外造成一次伤害。</t>
   </si>
   <si>
@@ -1014,7 +996,7 @@
     <t>痛殴</t>
   </si>
   <si>
-    <t>造成4点伤害两次。
+    <t xml:space="preserve">造成4点伤害两次。
 消耗你的手牌中随机一张攻击牌，并将它的伤害添加给这张牌。</t>
   </si>
   <si>
@@ -1024,7 +1006,7 @@
     <t>烙印</t>
   </si>
   <si>
-    <t>失去1点生命。
+    <t xml:space="preserve">失去1点生命。
 消耗1张牌。
 获得1点力量。</t>
   </si>
@@ -1035,7 +1017,7 @@
     <t>岿然不动</t>
   </si>
   <si>
-    <t>获得30点格挡。
+    <t xml:space="preserve">获得30点格挡。
 消耗。</t>
   </si>
   <si>
@@ -1048,7 +1030,7 @@
     <t>时候未到</t>
   </si>
   <si>
-    <t>回复10点生命。
+    <t xml:space="preserve">回复10点生命。
 消耗。</t>
   </si>
   <si>
@@ -1058,7 +1040,7 @@
     <t>祭品</t>
   </si>
   <si>
-    <t>失去6点生命。
+    <t xml:space="preserve">失去6点生命。
 获得2点能量。
 抽3张牌。
 消耗。</t>
@@ -1079,7 +1061,7 @@
     <t>原始力量</t>
   </si>
   <si>
-    <t>将手牌中的所有攻击牌变化为巨石。
+    <t xml:space="preserve">将手牌中的所有攻击牌变化为巨石。
 巨石：需要1颗斧头骰子，造成16点伤害。</t>
   </si>
   <si>
@@ -1089,7 +1071,7 @@
     <t>添柴</t>
   </si>
   <si>
-    <t>消耗所有手牌。
+    <t xml:space="preserve">消耗所有手牌。
 每消耗1张牌，将1张随机战士牌加入手牌。</t>
   </si>
   <si>
@@ -1114,7 +1096,7 @@
     <t>在你的回合开始时，失去1点生命并获得8点格挡。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210004,"target":"SELF","params":{"amount":1,"canKill":true},"children":[],"elseEffects":[],"id":"warriorEffect127"},{"type":210002,"target":"SELF","params":{"amount":8,"scale":true},"children":[],"elseEffects":[],"id":"warriorEffect128"}],"elseEffects":[],"id":"warriorEffect126"}]</t>
+    <t>[{"id":"abilityBuff20102","type":210010,"target":"SELF","params":{"status":200030,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>残酷</t>
@@ -1123,17 +1105,17 @@
     <t>有易伤状态的敌人额外受到25%的伤害。</t>
   </si>
   <si>
-    <t>[{"type":210047,"target":"SELF","params":{"kind":"VULNERABLE_BONUS","amount":0.25},"children":[],"elseEffects":[],"id":"warriorEffect129"}]</t>
+    <t>[{"id":"abilityBuff20103","type":210010,"target":"SELF","params":{"status":200031,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>黑暗之拥</t>
   </si>
   <si>
-    <t>每当有一张牌被消耗时，
+    <t xml:space="preserve">每当有一张牌被消耗时，
 抽1张牌。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_EXHAUST","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1,"untilNonAttack":false},"children":[],"elseEffects":[],"id":"warriorEffect131"}],"elseEffects":[],"id":"warriorEffect130"}]</t>
+    <t>[{"id":"abilityBuff20104","type":210010,"target":"SELF","params":{"status":200032,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>恶魔形态</t>
@@ -1142,7 +1124,7 @@
     <t>在你的回合开始时，获得2点力量。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210010,"target":"SELF","params":{"status":200001,"stacks":2,"duration":"COMBAT"},"children":[],"elseEffects":[],"id":"warriorEffect133"}],"elseEffects":[],"id":"warriorEffect132"}]</t>
+    <t>[{"id":"abilityBuff20105","type":210010,"target":"SELF","params":{"status":200033,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>地狱狂徒</t>
@@ -1151,7 +1133,7 @@
     <t>每当你抽到名字中含有“打击”的牌时，无需骰子对当前敌人打出这张牌。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_CARD_DRAWN","scope":"COMBAT","limit":0,"filter":{"strike":true}},"children":[{"type":210043,"target":"SELF","params":{"pile":"HAND","mode":"EVENT","exhaustAfter":false},"children":[],"elseEffects":[],"id":"warriorEffect135"}],"elseEffects":[],"id":"warriorEffect134"}]</t>
+    <t>[{"id":"abilityBuff20106","type":210010,"target":"SELF","params":{"status":200034,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>势不可当</t>
@@ -1160,7 +1142,7 @@
     <t>每当你获得格挡时，对敌人造成6点伤害。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_GAINED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210001,"target":"ENEMY","params":{"amount":6,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[],"id":"warriorEffect137"}],"elseEffects":[],"id":"warriorEffect136"}]</t>
+    <t>[{"id":"abilityBuff20107","type":210010,"target":"SELF","params":{"status":200035,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>薪火之源</t>
@@ -1169,7 +1151,7 @@
     <t>在回合开始时，获得1点能量。</t>
   </si>
   <si>
-    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[],"id":"warriorEffect139"}],"elseEffects":[],"id":"warriorEffect138"}]</t>
+    <t>[{"id":"abilityBuff20108","type":210010,"target":"SELF","params":{"status":200036,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>坚定不移</t>
@@ -1178,13 +1160,13 @@
     <t>翻倍你每回合第一次从卡牌中获得的格挡。</t>
   </si>
   <si>
-    <t>[{"type":210047,"target":"SELF","params":{"kind":"FIRST_BLOCK_DOUBLE","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect140"}]</t>
+    <t>[{"id":"abilityBuff20109","type":210010,"target":"SELF","params":{"status":200037,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>破击</t>
   </si>
   <si>
-    <t>造成20点伤害。
+    <t xml:space="preserve">造成20点伤害。
 给予5层易伤。</t>
   </si>
   <si>
@@ -1197,14 +1179,14 @@
     <t>腐化</t>
   </si>
   <si>
-    <t>本场战斗中，技能牌无需骰子。
+    <t xml:space="preserve">本场战斗中，技能牌无需骰子。
 每次打出技能牌后，将其消耗。</t>
   </si>
   <si>
     <t>[30001,30001,30001]</t>
   </si>
   <si>
-    <t>[{"type":210047,"target":"SELF","params":{"kind":"SKILL_FREE_EXHAUST","amount":1},"children":[],"elseEffects":[],"id":"warriorEffect143"}]</t>
+    <t>[{"id":"abilityBuff20111","type":210010,"target":"SELF","params":{"status":200038,"stacks":1,"duration":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>巨石</t>
@@ -1222,368 +1204,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="134"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1591,311 +1237,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2149,10 +1509,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L106"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.5916666666667" customWidth="1"/>
     <col min="3" max="3" width="113.833333333333" customWidth="1"/>
@@ -2160,7 +1519,7 @@
     <col min="8" max="8" width="24.5166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2198,7 +1557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -2236,7 +1595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -2274,7 +1633,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2312,7 +1671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -2350,7 +1709,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>20011</v>
       </c>
@@ -2385,7 +1744,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>20012</v>
       </c>
@@ -2420,7 +1779,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>20013</v>
       </c>
@@ -2455,7 +1814,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>20014</v>
       </c>
@@ -2490,7 +1849,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>20015</v>
       </c>
@@ -2525,7 +1884,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>20016</v>
       </c>
@@ -2560,7 +1919,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>20017</v>
       </c>
@@ -2595,7 +1954,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>20018</v>
       </c>
@@ -2630,7 +1989,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>20019</v>
       </c>
@@ -2665,7 +2024,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>20020</v>
       </c>
@@ -2700,7 +2059,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>20021</v>
       </c>
@@ -2735,7 +2094,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>20022</v>
       </c>
@@ -2770,7 +2129,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>20023</v>
       </c>
@@ -2805,7 +2164,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>20024</v>
       </c>
@@ -2840,7 +2199,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20025</v>
       </c>
@@ -2875,7 +2234,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20026</v>
       </c>
@@ -2910,7 +2269,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20027</v>
       </c>
@@ -2945,7 +2304,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20028</v>
       </c>
@@ -2980,7 +2339,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20029</v>
       </c>
@@ -3015,7 +2374,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>20030</v>
       </c>
@@ -3050,7 +2409,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>20031</v>
       </c>
@@ -3085,7 +2444,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>20032</v>
       </c>
@@ -3120,7 +2479,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>20033</v>
       </c>
@@ -3155,7 +2514,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>20034</v>
       </c>
@@ -3190,7 +2549,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>20035</v>
       </c>
@@ -3225,7 +2584,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>20036</v>
       </c>
@@ -3260,7 +2619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>20037</v>
       </c>
@@ -3295,7 +2654,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>20038</v>
       </c>
@@ -3330,7 +2689,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>20039</v>
       </c>
@@ -3365,7 +2724,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>20040</v>
       </c>
@@ -3400,7 +2759,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>20041</v>
       </c>
@@ -3435,7 +2794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>20042</v>
       </c>
@@ -3470,7 +2829,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>20043</v>
       </c>
@@ -3505,7 +2864,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>20044</v>
       </c>
@@ -3540,7 +2899,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>20045</v>
       </c>
@@ -3575,7 +2934,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>20046</v>
       </c>
@@ -3610,7 +2969,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>20048</v>
       </c>
@@ -3645,7 +3004,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>20049</v>
       </c>
@@ -3680,7 +3039,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>20050</v>
       </c>
@@ -3715,7 +3074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>20051</v>
       </c>
@@ -3750,7 +3109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>20052</v>
       </c>
@@ -3785,7 +3144,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>20053</v>
       </c>
@@ -3820,7 +3179,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>20054</v>
       </c>
@@ -3855,7 +3214,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>20055</v>
       </c>
@@ -3890,7 +3249,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>20056</v>
       </c>
@@ -3925,7 +3284,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>20057</v>
       </c>
@@ -3960,7 +3319,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>20058</v>
       </c>
@@ -3995,7 +3354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>20059</v>
       </c>
@@ -4030,7 +3389,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>20060</v>
       </c>
@@ -4065,7 +3424,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>20061</v>
       </c>
@@ -4100,7 +3459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>20062</v>
       </c>
@@ -4135,7 +3494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>20063</v>
       </c>
@@ -4170,7 +3529,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>20064</v>
       </c>
@@ -4205,7 +3564,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>20065</v>
       </c>
@@ -4240,7 +3599,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>20066</v>
       </c>
@@ -4275,7 +3634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>20067</v>
       </c>
@@ -4310,7 +3669,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>20068</v>
       </c>
@@ -4345,7 +3704,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>20069</v>
       </c>
@@ -4380,7 +3739,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>20070</v>
       </c>
@@ -4415,7 +3774,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>20071</v>
       </c>
@@ -4450,7 +3809,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>20072</v>
       </c>
@@ -4485,7 +3844,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>20073</v>
       </c>
@@ -4520,7 +3879,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>20074</v>
       </c>
@@ -4555,7 +3914,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>20075</v>
       </c>
@@ -4590,7 +3949,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>20076</v>
       </c>
@@ -4625,7 +3984,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>20077</v>
       </c>
@@ -4660,7 +4019,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>20078</v>
       </c>
@@ -4695,7 +4054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>20079</v>
       </c>
@@ -4730,7 +4089,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>20080</v>
       </c>
@@ -4765,7 +4124,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>20081</v>
       </c>
@@ -4800,7 +4159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>20082</v>
       </c>
@@ -4835,7 +4194,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>20083</v>
       </c>
@@ -4870,7 +4229,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>20084</v>
       </c>
@@ -4905,7 +4264,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>20085</v>
       </c>
@@ -4940,7 +4299,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>20086</v>
       </c>
@@ -4975,7 +4334,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>20087</v>
       </c>
@@ -5010,7 +4369,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>20088</v>
       </c>
@@ -5045,7 +4404,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>20089</v>
       </c>
@@ -5080,7 +4439,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>20090</v>
       </c>
@@ -5115,7 +4474,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>20091</v>
       </c>
@@ -5150,7 +4509,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>20092</v>
       </c>
@@ -5185,7 +4544,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>20093</v>
       </c>
@@ -5220,7 +4579,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>20094</v>
       </c>
@@ -5255,7 +4614,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>20095</v>
       </c>
@@ -5290,7 +4649,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>20096</v>
       </c>
@@ -5325,7 +4684,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>20097</v>
       </c>
@@ -5360,7 +4719,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>20098</v>
       </c>
@@ -5395,7 +4754,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>20099</v>
       </c>
@@ -5430,7 +4789,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>20100</v>
       </c>
@@ -5465,7 +4824,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>20101</v>
       </c>
@@ -5500,7 +4859,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>20102</v>
       </c>
@@ -5535,7 +4894,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>20103</v>
       </c>
@@ -5570,7 +4929,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>20104</v>
       </c>
@@ -5605,7 +4964,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>20105</v>
       </c>
@@ -5640,7 +4999,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>20106</v>
       </c>
@@ -5675,7 +5034,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>20107</v>
       </c>
@@ -5710,7 +5069,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>20108</v>
       </c>
@@ -5745,7 +5104,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>20109</v>
       </c>
@@ -5780,7 +5139,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>20110</v>
       </c>
@@ -5815,7 +5174,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>20111</v>
       </c>
@@ -5850,7 +5209,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>20112</v>
       </c>
@@ -5887,7 +5246,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>